--- a/research/traditional_assets/database/data/philippines/philippines_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_chemical_specialty.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1100723758054798</v>
+        <v>0.1098309448659661</v>
       </c>
       <c r="C2">
-        <v>1016.709818641053</v>
+        <v>1009.799061891473</v>
       </c>
       <c r="D2">
-        <v>971.8098186410531</v>
+        <v>975.4740618914734</v>
       </c>
       <c r="E2">
-        <v>-308.5</v>
+        <v>-297.925</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.575</v>
       </c>
       <c r="G2">
         <v>44.9</v>
@@ -1457,28 +1457,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5319225000000001</v>
       </c>
       <c r="N2">
-        <v>76.27777777777777</v>
+        <v>75.74585527777778</v>
       </c>
       <c r="O2">
-        <v>19.06944444444444</v>
+        <v>18.93646381944444</v>
       </c>
       <c r="P2">
-        <v>57.20833333333333</v>
+        <v>56.80939145833334</v>
       </c>
       <c r="Q2">
-        <v>67.70833333333333</v>
+        <v>67.30939145833334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1100723758054798</v>
+        <v>0.1105592877434002</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9423265434587135</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>143.4001715997683</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1098309448659661</v>
+        <v>0.1095895139264525</v>
       </c>
       <c r="C3">
-        <v>1009.799061891473</v>
+        <v>1002.916042042086</v>
       </c>
       <c r="D3">
-        <v>975.4740618914734</v>
+        <v>979.1660420420862</v>
       </c>
       <c r="E3">
-        <v>-297.925</v>
+        <v>-287.35</v>
       </c>
       <c r="F3">
-        <v>10.575</v>
+        <v>21.15</v>
       </c>
       <c r="G3">
         <v>44.9</v>
@@ -1539,28 +1539,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M3">
-        <v>0.5319225000000001</v>
+        <v>1.063845</v>
       </c>
       <c r="N3">
-        <v>75.74585527777778</v>
+        <v>75.21393277777777</v>
       </c>
       <c r="O3">
-        <v>18.93646381944444</v>
+        <v>18.80348319444444</v>
       </c>
       <c r="P3">
-        <v>56.80939145833334</v>
+        <v>56.41044958333333</v>
       </c>
       <c r="Q3">
-        <v>67.30939145833334</v>
+        <v>66.91044958333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1105592877434002</v>
+        <v>0.1110561366596454</v>
       </c>
       <c r="T3">
-        <v>0.9423265434587135</v>
+        <v>0.9495563005820733</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>143.4001715997683</v>
+        <v>71.70008579988415</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1095895139264525</v>
+        <v>0.1093480829869387</v>
       </c>
       <c r="C4">
-        <v>1002.916042042086</v>
+        <v>996.0610752257581</v>
       </c>
       <c r="D4">
-        <v>979.1660420420862</v>
+        <v>982.8860752257581</v>
       </c>
       <c r="E4">
-        <v>-287.35</v>
+        <v>-276.775</v>
       </c>
       <c r="F4">
-        <v>21.15</v>
+        <v>31.725</v>
       </c>
       <c r="G4">
         <v>44.9</v>
@@ -1621,28 +1621,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M4">
-        <v>1.063845</v>
+        <v>1.5957675</v>
       </c>
       <c r="N4">
-        <v>75.21393277777777</v>
+        <v>74.68201027777778</v>
       </c>
       <c r="O4">
-        <v>18.80348319444444</v>
+        <v>18.67050256944444</v>
       </c>
       <c r="P4">
-        <v>56.41044958333333</v>
+        <v>56.01150770833333</v>
       </c>
       <c r="Q4">
-        <v>66.91044958333333</v>
+        <v>66.51150770833334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1110561366596454</v>
+        <v>0.111563229883442</v>
       </c>
       <c r="T4">
-        <v>0.9495563005820733</v>
+        <v>0.9569351248626156</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.70008579988415</v>
+        <v>47.80005719992279</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1093480829869387</v>
+        <v>0.109106652047425</v>
       </c>
       <c r="C5">
-        <v>996.0610752257581</v>
+        <v>989.2344823978656</v>
       </c>
       <c r="D5">
-        <v>982.8860752257581</v>
+        <v>986.6344823978654</v>
       </c>
       <c r="E5">
-        <v>-276.775</v>
+        <v>-266.2</v>
       </c>
       <c r="F5">
-        <v>31.725</v>
+        <v>42.3</v>
       </c>
       <c r="G5">
         <v>44.9</v>
@@ -1703,28 +1703,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M5">
-        <v>1.5957675</v>
+        <v>2.12769</v>
       </c>
       <c r="N5">
-        <v>74.68201027777778</v>
+        <v>74.15008777777777</v>
       </c>
       <c r="O5">
-        <v>18.67050256944444</v>
+        <v>18.53752194444444</v>
       </c>
       <c r="P5">
-        <v>56.01150770833333</v>
+        <v>55.61256583333333</v>
       </c>
       <c r="Q5">
-        <v>66.51150770833334</v>
+        <v>66.11256583333332</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.111563229883442</v>
+        <v>0.1120808875494011</v>
       </c>
       <c r="T5">
-        <v>0.9569351248626156</v>
+        <v>0.9644676746490027</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.80005719992279</v>
+        <v>35.85004289994207</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.109106652047425</v>
+        <v>0.1088652211079114</v>
       </c>
       <c r="C6">
-        <v>989.2344823978656</v>
+        <v>982.4365894286063</v>
       </c>
       <c r="D6">
-        <v>986.6344823978654</v>
+        <v>990.4115894286064</v>
       </c>
       <c r="E6">
-        <v>-266.2</v>
+        <v>-255.625</v>
       </c>
       <c r="F6">
-        <v>42.3</v>
+        <v>52.875</v>
       </c>
       <c r="G6">
         <v>44.9</v>
@@ -1785,28 +1785,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M6">
-        <v>2.12769</v>
+        <v>2.6596125</v>
       </c>
       <c r="N6">
-        <v>74.15008777777777</v>
+        <v>73.61816527777778</v>
       </c>
       <c r="O6">
-        <v>18.53752194444444</v>
+        <v>18.40454131944444</v>
       </c>
       <c r="P6">
-        <v>55.61256583333333</v>
+        <v>55.21362395833333</v>
       </c>
       <c r="Q6">
-        <v>66.11256583333332</v>
+        <v>65.71362395833333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1120808875494011</v>
+        <v>0.1126094432714856</v>
       </c>
       <c r="T6">
-        <v>0.9644676746490027</v>
+        <v>0.9721588044308928</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.85004289994207</v>
+        <v>28.68003431995367</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1088652211079114</v>
+        <v>0.1086237901683976</v>
       </c>
       <c r="C7">
-        <v>982.4365894286063</v>
+        <v>975.667727197437</v>
       </c>
       <c r="D7">
-        <v>990.4115894286064</v>
+        <v>994.2177271974369</v>
       </c>
       <c r="E7">
-        <v>-255.625</v>
+        <v>-245.05</v>
       </c>
       <c r="F7">
-        <v>52.875</v>
+        <v>63.45</v>
       </c>
       <c r="G7">
         <v>44.9</v>
@@ -1867,28 +1867,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M7">
-        <v>2.6596125</v>
+        <v>3.191535</v>
       </c>
       <c r="N7">
-        <v>73.61816527777778</v>
+        <v>73.08624277777777</v>
       </c>
       <c r="O7">
-        <v>18.40454131944444</v>
+        <v>18.27156069444444</v>
       </c>
       <c r="P7">
-        <v>55.21362395833333</v>
+        <v>54.81468208333332</v>
       </c>
       <c r="Q7">
-        <v>65.71362395833333</v>
+        <v>65.31468208333332</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1126094432714856</v>
+        <v>0.1131492448599975</v>
       </c>
       <c r="T7">
-        <v>0.9721588044308928</v>
+        <v>0.9800135752719719</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.68003431995367</v>
+        <v>23.90002859996139</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1086237901683976</v>
+        <v>0.108382359228884</v>
       </c>
       <c r="C8">
-        <v>975.667727197437</v>
+        <v>968.9282316896941</v>
       </c>
       <c r="D8">
-        <v>994.2177271974369</v>
+        <v>998.053231689694</v>
       </c>
       <c r="E8">
-        <v>-245.05</v>
+        <v>-234.475</v>
       </c>
       <c r="F8">
-        <v>63.45</v>
+        <v>74.02499999999999</v>
       </c>
       <c r="G8">
         <v>44.9</v>
@@ -1949,28 +1949,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M8">
-        <v>3.191535</v>
+        <v>3.723457499999999</v>
       </c>
       <c r="N8">
-        <v>73.08624277777777</v>
+        <v>72.55432027777778</v>
       </c>
       <c r="O8">
-        <v>18.27156069444444</v>
+        <v>18.13858006944444</v>
       </c>
       <c r="P8">
-        <v>54.81468208333332</v>
+        <v>54.41574020833333</v>
       </c>
       <c r="Q8">
-        <v>65.31468208333332</v>
+        <v>64.91574020833333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1131492448599975</v>
+        <v>0.1137006550848215</v>
       </c>
       <c r="T8">
-        <v>0.9800135752719719</v>
+        <v>0.9880372659160849</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.90002859996139</v>
+        <v>20.48573879996691</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.108382359228884</v>
+        <v>0.1081409282893702</v>
       </c>
       <c r="C9">
-        <v>968.9282316896944</v>
+        <v>962.218444095468</v>
       </c>
       <c r="D9">
-        <v>998.0532316896943</v>
+        <v>1001.918444095468</v>
       </c>
       <c r="E9">
-        <v>-234.475</v>
+        <v>-223.9</v>
       </c>
       <c r="F9">
-        <v>74.02500000000001</v>
+        <v>84.60000000000001</v>
       </c>
       <c r="G9">
         <v>44.9</v>
@@ -2031,28 +2031,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M9">
-        <v>3.7234575</v>
+        <v>4.255380000000001</v>
       </c>
       <c r="N9">
-        <v>72.55432027777778</v>
+        <v>72.02239777777777</v>
       </c>
       <c r="O9">
-        <v>18.13858006944444</v>
+        <v>18.00559944444444</v>
       </c>
       <c r="P9">
-        <v>54.41574020833333</v>
+        <v>54.01679833333333</v>
       </c>
       <c r="Q9">
-        <v>64.91574020833333</v>
+        <v>64.51679833333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1137006550848215</v>
+        <v>0.1142640524884459</v>
       </c>
       <c r="T9">
-        <v>0.9880372659160849</v>
+        <v>0.9962353846176788</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.4857387999669</v>
+        <v>17.92502144997104</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1081409282893702</v>
+        <v>0.1078994973498566</v>
       </c>
       <c r="C10">
-        <v>962.218444095468</v>
+        <v>955.5387109107739</v>
       </c>
       <c r="D10">
-        <v>1001.918444095468</v>
+        <v>1005.813710910774</v>
       </c>
       <c r="E10">
-        <v>-223.9</v>
+        <v>-213.325</v>
       </c>
       <c r="F10">
-        <v>84.60000000000001</v>
+        <v>95.175</v>
       </c>
       <c r="G10">
         <v>44.9</v>
@@ -2113,28 +2113,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M10">
-        <v>4.255380000000001</v>
+        <v>4.7873025</v>
       </c>
       <c r="N10">
-        <v>72.02239777777777</v>
+        <v>71.49047527777778</v>
       </c>
       <c r="O10">
-        <v>18.00559944444444</v>
+        <v>17.87261881944444</v>
       </c>
       <c r="P10">
-        <v>54.01679833333333</v>
+        <v>53.61785645833334</v>
       </c>
       <c r="Q10">
-        <v>64.51679833333333</v>
+        <v>64.11785645833334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1142640524884459</v>
+        <v>0.1148398322525896</v>
       </c>
       <c r="T10">
-        <v>0.9962353846176788</v>
+        <v>1.004613681752275</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.92502144997104</v>
+        <v>15.93335239997426</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1078994973498566</v>
+        <v>0.1076580664103429</v>
       </c>
       <c r="C11">
-        <v>955.5387109107739</v>
+        <v>948.8893840410988</v>
       </c>
       <c r="D11">
-        <v>1005.813710910774</v>
+        <v>1009.739384041099</v>
       </c>
       <c r="E11">
-        <v>-213.325</v>
+        <v>-202.75</v>
       </c>
       <c r="F11">
-        <v>95.175</v>
+        <v>105.75</v>
       </c>
       <c r="G11">
         <v>44.9</v>
@@ -2195,28 +2195,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M11">
-        <v>4.7873025</v>
+        <v>5.319224999999999</v>
       </c>
       <c r="N11">
-        <v>71.49047527777778</v>
+        <v>70.95855277777777</v>
       </c>
       <c r="O11">
-        <v>17.87261881944444</v>
+        <v>17.73963819444444</v>
       </c>
       <c r="P11">
-        <v>53.61785645833334</v>
+        <v>53.21891458333333</v>
       </c>
       <c r="Q11">
-        <v>64.11785645833334</v>
+        <v>63.71891458333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1148398322525896</v>
+        <v>0.1154284071226032</v>
       </c>
       <c r="T11">
-        <v>1.004613681752275</v>
+        <v>1.013178163267639</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.93335239997426</v>
+        <v>14.34001715997683</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1076580664103429</v>
+        <v>0.1074166354708291</v>
       </c>
       <c r="C12">
-        <v>948.8893840410988</v>
+        <v>942.2708209073808</v>
       </c>
       <c r="D12">
-        <v>1009.739384041099</v>
+        <v>1013.695820907381</v>
       </c>
       <c r="E12">
-        <v>-202.75</v>
+        <v>-192.175</v>
       </c>
       <c r="F12">
-        <v>105.75</v>
+        <v>116.325</v>
       </c>
       <c r="G12">
         <v>44.9</v>
@@ -2277,28 +2277,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M12">
-        <v>5.319224999999999</v>
+        <v>5.8511475</v>
       </c>
       <c r="N12">
-        <v>70.95855277777777</v>
+        <v>70.42663027777778</v>
       </c>
       <c r="O12">
-        <v>17.73963819444444</v>
+        <v>17.60665756944444</v>
       </c>
       <c r="P12">
-        <v>53.21891458333333</v>
+        <v>52.81997270833333</v>
       </c>
       <c r="Q12">
-        <v>63.71891458333333</v>
+        <v>63.31997270833333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1154284071226032</v>
+        <v>0.1160302083941901</v>
       </c>
       <c r="T12">
-        <v>1.013178163267639</v>
+        <v>1.021935105041776</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.34001715997683</v>
+        <v>13.03637923634258</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1074166354708291</v>
+        <v>0.1073102045313155</v>
       </c>
       <c r="C13">
-        <v>942.2708209073808</v>
+        <v>933.4498160277409</v>
       </c>
       <c r="D13">
-        <v>1013.695820907381</v>
+        <v>1015.449816027741</v>
       </c>
       <c r="E13">
-        <v>-192.175</v>
+        <v>-181.6</v>
       </c>
       <c r="F13">
-        <v>116.325</v>
+        <v>126.9</v>
       </c>
       <c r="G13">
         <v>44.9</v>
@@ -2359,45 +2359,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M13">
-        <v>5.8511475</v>
+        <v>6.57342</v>
       </c>
       <c r="N13">
-        <v>70.42663027777778</v>
+        <v>69.70435777777777</v>
       </c>
       <c r="O13">
-        <v>17.60665756944444</v>
+        <v>17.42608944444444</v>
       </c>
       <c r="P13">
-        <v>52.81997270833333</v>
+        <v>52.27826833333333</v>
       </c>
       <c r="Q13">
-        <v>63.31997270833333</v>
+        <v>62.77826833333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1160302083941901</v>
+        <v>0.1166456869674039</v>
       </c>
       <c r="T13">
-        <v>1.021935105041776</v>
+        <v>1.030891068219871</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.03637923634258</v>
+        <v>11.60397141484612</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1073102045313155</v>
+        <v>0.1070800235918018</v>
       </c>
       <c r="C14">
-        <v>933.4498160277409</v>
+        <v>926.6890637871612</v>
       </c>
       <c r="D14">
-        <v>1015.449816027741</v>
+        <v>1019.264063787161</v>
       </c>
       <c r="E14">
-        <v>-181.6</v>
+        <v>-171.025</v>
       </c>
       <c r="F14">
-        <v>126.9</v>
+        <v>137.475</v>
       </c>
       <c r="G14">
         <v>44.9</v>
@@ -2441,28 +2441,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M14">
-        <v>6.57342</v>
+        <v>7.121205</v>
       </c>
       <c r="N14">
-        <v>69.70435777777777</v>
+        <v>69.15657277777777</v>
       </c>
       <c r="O14">
-        <v>17.42608944444444</v>
+        <v>17.28914319444444</v>
       </c>
       <c r="P14">
-        <v>52.27826833333333</v>
+        <v>51.86742958333333</v>
       </c>
       <c r="Q14">
-        <v>62.77826833333333</v>
+        <v>62.36742958333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1166456869674039</v>
+        <v>0.1172753144733354</v>
       </c>
       <c r="T14">
-        <v>1.030891068219871</v>
+        <v>1.040052915608956</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.60397141484612</v>
+        <v>10.71135822908872</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1070800235918018</v>
+        <v>0.1068498426522881</v>
       </c>
       <c r="C15">
-        <v>926.6890637871612</v>
+        <v>919.9570738527455</v>
       </c>
       <c r="D15">
-        <v>1019.264063787161</v>
+        <v>1023.107073852745</v>
       </c>
       <c r="E15">
-        <v>-171.025</v>
+        <v>-160.45</v>
       </c>
       <c r="F15">
-        <v>137.475</v>
+        <v>148.05</v>
       </c>
       <c r="G15">
         <v>44.9</v>
@@ -2523,28 +2523,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M15">
-        <v>7.121205</v>
+        <v>7.66899</v>
       </c>
       <c r="N15">
-        <v>69.15657277777777</v>
+        <v>68.60878777777778</v>
       </c>
       <c r="O15">
-        <v>17.28914319444444</v>
+        <v>17.15219694444444</v>
       </c>
       <c r="P15">
-        <v>51.86742958333333</v>
+        <v>51.45659083333334</v>
       </c>
       <c r="Q15">
-        <v>62.36742958333333</v>
+        <v>61.95659083333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1172753144733354</v>
+        <v>0.1179195844794047</v>
       </c>
       <c r="T15">
-        <v>1.040052915608956</v>
+        <v>1.049427829216392</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.71135822908872</v>
+        <v>9.946261212725245</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1068498426522881</v>
+        <v>0.1068109117127744</v>
       </c>
       <c r="C16">
-        <v>919.9570738527455</v>
+        <v>910.0349164097577</v>
       </c>
       <c r="D16">
-        <v>1023.107073852745</v>
+        <v>1023.759916409758</v>
       </c>
       <c r="E16">
-        <v>-160.45</v>
+        <v>-149.875</v>
       </c>
       <c r="F16">
-        <v>148.05</v>
+        <v>158.625</v>
       </c>
       <c r="G16">
         <v>44.9</v>
@@ -2605,45 +2605,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M16">
-        <v>7.66899</v>
+        <v>8.486437500000001</v>
       </c>
       <c r="N16">
-        <v>68.60878777777778</v>
+        <v>67.79134027777778</v>
       </c>
       <c r="O16">
-        <v>17.15219694444444</v>
+        <v>16.94783506944444</v>
       </c>
       <c r="P16">
-        <v>51.45659083333334</v>
+        <v>50.84350520833333</v>
       </c>
       <c r="Q16">
-        <v>61.95659083333334</v>
+        <v>61.34350520833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1179195844794047</v>
+        <v>0.1185790137797345</v>
       </c>
       <c r="T16">
-        <v>1.049427829216392</v>
+        <v>1.059023329026356</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.946261212725245</v>
+        <v>8.988197671611648</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1068109117127744</v>
+        <v>0.1065934807732606</v>
       </c>
       <c r="C17">
-        <v>910.0349164097577</v>
+        <v>903.1214452057759</v>
       </c>
       <c r="D17">
-        <v>1023.759916409758</v>
+        <v>1027.421445205776</v>
       </c>
       <c r="E17">
-        <v>-149.875</v>
+        <v>-139.3</v>
       </c>
       <c r="F17">
-        <v>158.625</v>
+        <v>169.2</v>
       </c>
       <c r="G17">
         <v>44.9</v>
@@ -2687,28 +2687,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M17">
-        <v>8.486437499999999</v>
+        <v>9.052200000000001</v>
       </c>
       <c r="N17">
-        <v>67.79134027777778</v>
+        <v>67.22557777777777</v>
       </c>
       <c r="O17">
-        <v>16.94783506944444</v>
+        <v>16.80639444444444</v>
       </c>
       <c r="P17">
-        <v>50.84350520833333</v>
+        <v>50.41918333333333</v>
       </c>
       <c r="Q17">
-        <v>61.34350520833333</v>
+        <v>60.91918333333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1185790137797345</v>
+        <v>0.1192541437776913</v>
       </c>
       <c r="T17">
-        <v>1.059023329026356</v>
+        <v>1.068847293117509</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.988197671611649</v>
+        <v>8.426435317135919</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1065934807732606</v>
+        <v>0.106376049833747</v>
       </c>
       <c r="C18">
-        <v>903.1214452057759</v>
+        <v>896.2342592960093</v>
       </c>
       <c r="D18">
-        <v>1027.421445205776</v>
+        <v>1031.109259296009</v>
       </c>
       <c r="E18">
-        <v>-139.3</v>
+        <v>-128.725</v>
       </c>
       <c r="F18">
-        <v>169.2</v>
+        <v>179.775</v>
       </c>
       <c r="G18">
         <v>44.9</v>
@@ -2769,28 +2769,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M18">
-        <v>9.052200000000001</v>
+        <v>9.617962500000001</v>
       </c>
       <c r="N18">
-        <v>67.22557777777777</v>
+        <v>66.65981527777777</v>
       </c>
       <c r="O18">
-        <v>16.80639444444444</v>
+        <v>16.66495381944444</v>
       </c>
       <c r="P18">
-        <v>50.41918333333333</v>
+        <v>49.99486145833333</v>
       </c>
       <c r="Q18">
-        <v>60.91918333333333</v>
+        <v>60.49486145833333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1192541437776913</v>
+        <v>0.1199455419683698</v>
       </c>
       <c r="T18">
-        <v>1.068847293117509</v>
+        <v>1.078907979234956</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.426435317135919</v>
+        <v>7.930762651422041</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.106376049833747</v>
+        <v>0.1062666188942333</v>
       </c>
       <c r="C19">
-        <v>896.2342592960093</v>
+        <v>887.5253344470513</v>
       </c>
       <c r="D19">
-        <v>1031.109259296009</v>
+        <v>1032.975334447051</v>
       </c>
       <c r="E19">
-        <v>-128.725</v>
+        <v>-118.15</v>
       </c>
       <c r="F19">
-        <v>179.775</v>
+        <v>190.35</v>
       </c>
       <c r="G19">
         <v>44.9</v>
@@ -2851,45 +2851,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M19">
-        <v>9.617962500000001</v>
+        <v>10.336005</v>
       </c>
       <c r="N19">
-        <v>66.65981527777777</v>
+        <v>65.94177277777777</v>
       </c>
       <c r="O19">
-        <v>16.66495381944444</v>
+        <v>16.48544319444444</v>
       </c>
       <c r="P19">
-        <v>49.99486145833333</v>
+        <v>49.45632958333333</v>
       </c>
       <c r="Q19">
-        <v>60.49486145833333</v>
+        <v>59.95632958333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1199455419683698</v>
+        <v>0.1206538035295527</v>
       </c>
       <c r="T19">
-        <v>1.078907979234956</v>
+        <v>1.089214047940633</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.930762651422041</v>
+        <v>7.379812391516622</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1062666188942333</v>
+        <v>0.1060551879547196</v>
       </c>
       <c r="C20">
-        <v>887.525334447051</v>
+        <v>880.574967493101</v>
       </c>
       <c r="D20">
-        <v>1032.975334447051</v>
+        <v>1036.599967493101</v>
       </c>
       <c r="E20">
-        <v>-118.15</v>
+        <v>-107.575</v>
       </c>
       <c r="F20">
-        <v>190.35</v>
+        <v>200.925</v>
       </c>
       <c r="G20">
         <v>44.9</v>
@@ -2933,28 +2933,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M20">
-        <v>10.336005</v>
+        <v>10.9102275</v>
       </c>
       <c r="N20">
-        <v>65.94177277777777</v>
+        <v>65.36755027777777</v>
       </c>
       <c r="O20">
-        <v>16.48544319444444</v>
+        <v>16.34188756944444</v>
       </c>
       <c r="P20">
-        <v>49.45632958333333</v>
+        <v>49.02566270833333</v>
       </c>
       <c r="Q20">
-        <v>59.95632958333333</v>
+        <v>59.52566270833333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1206538035295527</v>
+        <v>0.121379553030518</v>
       </c>
       <c r="T20">
-        <v>1.089214047940633</v>
+        <v>1.099774587478549</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.379812391516623</v>
+        <v>6.991401213015747</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1060551879547196</v>
+        <v>0.1058437570152059</v>
       </c>
       <c r="C21">
-        <v>880.574967493101</v>
+        <v>873.6501272419559</v>
       </c>
       <c r="D21">
-        <v>1036.599967493101</v>
+        <v>1040.250127241956</v>
       </c>
       <c r="E21">
-        <v>-107.575</v>
+        <v>-97</v>
       </c>
       <c r="F21">
-        <v>200.925</v>
+        <v>211.5</v>
       </c>
       <c r="G21">
         <v>44.9</v>
@@ -3015,28 +3015,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M21">
-        <v>10.9102275</v>
+        <v>11.48445</v>
       </c>
       <c r="N21">
-        <v>65.36755027777777</v>
+        <v>64.79332777777778</v>
       </c>
       <c r="O21">
-        <v>16.34188756944444</v>
+        <v>16.19833194444444</v>
       </c>
       <c r="P21">
-        <v>49.02566270833333</v>
+        <v>48.59499583333333</v>
       </c>
       <c r="Q21">
-        <v>59.52566270833333</v>
+        <v>59.09499583333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.121379553030518</v>
+        <v>0.1221234462690073</v>
       </c>
       <c r="T21">
-        <v>1.099774587478549</v>
+        <v>1.110599140504912</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.991401213015747</v>
+        <v>6.64183115236496</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1058437570152059</v>
+        <v>0.1056323260756922</v>
       </c>
       <c r="C22">
-        <v>873.6501272419559</v>
+        <v>866.7510843065998</v>
       </c>
       <c r="D22">
-        <v>1040.250127241956</v>
+        <v>1043.9260843066</v>
       </c>
       <c r="E22">
-        <v>-97</v>
+        <v>-86.42499999999998</v>
       </c>
       <c r="F22">
-        <v>211.5</v>
+        <v>222.075</v>
       </c>
       <c r="G22">
         <v>44.9</v>
@@ -3097,28 +3097,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M22">
-        <v>11.48445</v>
+        <v>12.0586725</v>
       </c>
       <c r="N22">
-        <v>64.79332777777778</v>
+        <v>64.21910527777777</v>
       </c>
       <c r="O22">
-        <v>16.19833194444444</v>
+        <v>16.05477631944444</v>
       </c>
       <c r="P22">
-        <v>48.59499583333333</v>
+        <v>48.16432895833333</v>
       </c>
       <c r="Q22">
-        <v>59.09499583333333</v>
+        <v>58.66432895833333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1221234462690073</v>
+        <v>0.1228861722477116</v>
       </c>
       <c r="T22">
-        <v>1.110599140504912</v>
+        <v>1.121697732848399</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.64183115236496</v>
+        <v>6.325553478442819</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1056323260756922</v>
+        <v>0.1055858951361784</v>
       </c>
       <c r="C23">
-        <v>866.7510843065998</v>
+        <v>856.9868184900862</v>
       </c>
       <c r="D23">
-        <v>1043.9260843066</v>
+        <v>1044.736818490086</v>
       </c>
       <c r="E23">
-        <v>-86.42500000000001</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="F23">
-        <v>222.075</v>
+        <v>232.65</v>
       </c>
       <c r="G23">
         <v>44.9</v>
@@ -3179,45 +3179,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M23">
-        <v>12.0586725</v>
+        <v>12.865545</v>
       </c>
       <c r="N23">
-        <v>64.21910527777777</v>
+        <v>63.41223277777777</v>
       </c>
       <c r="O23">
-        <v>16.05477631944444</v>
+        <v>15.85305819444444</v>
       </c>
       <c r="P23">
-        <v>48.16432895833333</v>
+        <v>47.55917458333333</v>
       </c>
       <c r="Q23">
-        <v>58.66432895833333</v>
+        <v>58.05917458333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1228861722477116</v>
+        <v>0.1236684553027929</v>
       </c>
       <c r="T23">
-        <v>1.121697732848399</v>
+        <v>1.133080904482744</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.32555347844282</v>
+        <v>5.928841551428857</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1055858951361784</v>
+        <v>0.1053819641966648</v>
       </c>
       <c r="C24">
-        <v>856.9868184900862</v>
+        <v>849.9876348266538</v>
       </c>
       <c r="D24">
-        <v>1044.736818490086</v>
+        <v>1048.312634826654</v>
       </c>
       <c r="E24">
-        <v>-75.84999999999999</v>
+        <v>-65.27499999999998</v>
       </c>
       <c r="F24">
-        <v>232.65</v>
+        <v>243.225</v>
       </c>
       <c r="G24">
         <v>44.9</v>
@@ -3261,28 +3261,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M24">
-        <v>12.865545</v>
+        <v>13.4503425</v>
       </c>
       <c r="N24">
-        <v>63.41223277777777</v>
+        <v>62.82743527777777</v>
       </c>
       <c r="O24">
-        <v>15.85305819444444</v>
+        <v>15.70685881944444</v>
       </c>
       <c r="P24">
-        <v>47.55917458333333</v>
+        <v>47.12057645833332</v>
       </c>
       <c r="Q24">
-        <v>58.05917458333333</v>
+        <v>57.62057645833332</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1236684553027929</v>
+        <v>0.1244710573982659</v>
       </c>
       <c r="T24">
-        <v>1.133080904482744</v>
+        <v>1.144759742912787</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.928841551428857</v>
+        <v>5.671065831801514</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1053819641966648</v>
+        <v>0.1051780332571511</v>
       </c>
       <c r="C25">
-        <v>849.9876348266538</v>
+        <v>843.0130130944626</v>
       </c>
       <c r="D25">
-        <v>1048.312634826654</v>
+        <v>1051.913013094462</v>
       </c>
       <c r="E25">
-        <v>-65.27499999999998</v>
+        <v>-54.69999999999999</v>
       </c>
       <c r="F25">
-        <v>243.225</v>
+        <v>253.8</v>
       </c>
       <c r="G25">
         <v>44.9</v>
@@ -3343,28 +3343,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M25">
-        <v>13.4503425</v>
+        <v>14.03514</v>
       </c>
       <c r="N25">
-        <v>62.82743527777777</v>
+        <v>62.24263777777777</v>
       </c>
       <c r="O25">
-        <v>15.70685881944444</v>
+        <v>15.56065944444444</v>
       </c>
       <c r="P25">
-        <v>47.12057645833332</v>
+        <v>46.68197833333333</v>
       </c>
       <c r="Q25">
-        <v>57.62057645833332</v>
+        <v>57.18197833333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1244710573982659</v>
+        <v>0.1252947806015146</v>
       </c>
       <c r="T25">
-        <v>1.144759742912787</v>
+        <v>1.156745919196252</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.671065831801514</v>
+        <v>5.434771422143118</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1051780332571511</v>
+        <v>0.1049741023176374</v>
       </c>
       <c r="C26">
-        <v>843.0130130944626</v>
+        <v>836.0632072359053</v>
       </c>
       <c r="D26">
-        <v>1051.913013094462</v>
+        <v>1055.538207235905</v>
       </c>
       <c r="E26">
-        <v>-54.70000000000002</v>
+        <v>-44.125</v>
       </c>
       <c r="F26">
-        <v>253.8</v>
+        <v>264.375</v>
       </c>
       <c r="G26">
         <v>44.9</v>
@@ -3425,28 +3425,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M26">
-        <v>14.03514</v>
+        <v>14.6199375</v>
       </c>
       <c r="N26">
-        <v>62.24263777777777</v>
+        <v>61.65784027777777</v>
       </c>
       <c r="O26">
-        <v>15.56065944444444</v>
+        <v>15.41446006944444</v>
       </c>
       <c r="P26">
-        <v>46.68197833333333</v>
+        <v>46.24338020833333</v>
       </c>
       <c r="Q26">
-        <v>57.18197833333333</v>
+        <v>56.74338020833333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1252947806015146</v>
+        <v>0.1261404697568498</v>
       </c>
       <c r="T26">
-        <v>1.156745919196252</v>
+        <v>1.169051726847276</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.434771422143119</v>
+        <v>5.217380565257394</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1049741023176374</v>
+        <v>0.1047701713781237</v>
       </c>
       <c r="C27">
-        <v>836.0632072359053</v>
+        <v>829.1384747061145</v>
       </c>
       <c r="D27">
-        <v>1055.538207235905</v>
+        <v>1059.188474706114</v>
       </c>
       <c r="E27">
-        <v>-44.125</v>
+        <v>-33.55000000000001</v>
       </c>
       <c r="F27">
-        <v>264.375</v>
+        <v>274.95</v>
       </c>
       <c r="G27">
         <v>44.9</v>
@@ -3507,28 +3507,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M27">
-        <v>14.6199375</v>
+        <v>15.204735</v>
       </c>
       <c r="N27">
-        <v>61.65784027777777</v>
+        <v>61.07304277777777</v>
       </c>
       <c r="O27">
-        <v>15.41446006944444</v>
+        <v>15.26826069444444</v>
       </c>
       <c r="P27">
-        <v>46.24338020833333</v>
+        <v>45.80478208333333</v>
       </c>
       <c r="Q27">
-        <v>56.74338020833333</v>
+        <v>56.30478208333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1261404697568498</v>
+        <v>0.1270090153758428</v>
       </c>
       <c r="T27">
-        <v>1.169051726847276</v>
+        <v>1.181690123894274</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.217380565257394</v>
+        <v>5.016712081978263</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1047701713781237</v>
+        <v>0.10456624043861</v>
       </c>
       <c r="C28">
-        <v>829.1384747061145</v>
+        <v>822.2390765339114</v>
       </c>
       <c r="D28">
-        <v>1059.188474706114</v>
+        <v>1062.864076533911</v>
       </c>
       <c r="E28">
-        <v>-33.55000000000001</v>
+        <v>-22.97499999999997</v>
       </c>
       <c r="F28">
-        <v>274.95</v>
+        <v>285.525</v>
       </c>
       <c r="G28">
         <v>44.9</v>
@@ -3589,28 +3589,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M28">
-        <v>15.204735</v>
+        <v>15.7895325</v>
       </c>
       <c r="N28">
-        <v>61.07304277777777</v>
+        <v>60.48824527777777</v>
       </c>
       <c r="O28">
-        <v>15.26826069444444</v>
+        <v>15.12206131944444</v>
       </c>
       <c r="P28">
-        <v>45.80478208333333</v>
+        <v>45.36618395833333</v>
       </c>
       <c r="Q28">
-        <v>56.30478208333333</v>
+        <v>55.86618395833333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1270090153758428</v>
+        <v>0.1279013567652191</v>
       </c>
       <c r="T28">
-        <v>1.181690123894274</v>
+        <v>1.194674778394614</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.016712081978263</v>
+        <v>4.830907930793883</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.10456624043861</v>
+        <v>0.1043623094990963</v>
       </c>
       <c r="C29">
-        <v>822.2390765339114</v>
+        <v>815.3652773840294</v>
       </c>
       <c r="D29">
-        <v>1062.864076533911</v>
+        <v>1066.565277384029</v>
       </c>
       <c r="E29">
-        <v>-22.97499999999997</v>
+        <v>-12.39999999999998</v>
       </c>
       <c r="F29">
-        <v>285.525</v>
+        <v>296.1</v>
       </c>
       <c r="G29">
         <v>44.9</v>
@@ -3671,28 +3671,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M29">
-        <v>15.7895325</v>
+        <v>16.37433</v>
       </c>
       <c r="N29">
-        <v>60.48824527777777</v>
+        <v>59.90344777777777</v>
       </c>
       <c r="O29">
-        <v>15.12206131944444</v>
+        <v>14.97586194444444</v>
       </c>
       <c r="P29">
-        <v>45.36618395833333</v>
+        <v>44.92758583333332</v>
       </c>
       <c r="Q29">
-        <v>55.86618395833333</v>
+        <v>55.42758583333332</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1279013567652191</v>
+        <v>0.1288184854154115</v>
       </c>
       <c r="T29">
-        <v>1.194674778394614</v>
+        <v>1.208020117742185</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.830907930793883</v>
+        <v>4.658375504694101</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1043623094990963</v>
+        <v>0.1047021285595826</v>
       </c>
       <c r="C30">
-        <v>815.3652773840294</v>
+        <v>798.6370326818228</v>
       </c>
       <c r="D30">
-        <v>1066.565277384029</v>
+        <v>1060.412032681823</v>
       </c>
       <c r="E30">
-        <v>-12.39999999999998</v>
+        <v>-1.824999999999989</v>
       </c>
       <c r="F30">
-        <v>296.1</v>
+        <v>306.675</v>
       </c>
       <c r="G30">
         <v>44.9</v>
@@ -3753,45 +3753,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M30">
-        <v>16.37433</v>
+        <v>17.725815</v>
       </c>
       <c r="N30">
-        <v>59.90344777777777</v>
+        <v>58.55196277777777</v>
       </c>
       <c r="O30">
-        <v>14.97586194444444</v>
+        <v>14.63799069444444</v>
       </c>
       <c r="P30">
-        <v>44.92758583333332</v>
+        <v>43.91397208333333</v>
       </c>
       <c r="Q30">
-        <v>55.42758583333332</v>
+        <v>54.41397208333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1288184854154115</v>
+        <v>0.1297614486754684</v>
       </c>
       <c r="T30">
-        <v>1.208020117742185</v>
+        <v>1.221741382141801</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.658375504694101</v>
+        <v>4.303202858530216</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1047021285595826</v>
+        <v>0.1045169476200689</v>
       </c>
       <c r="C31">
-        <v>798.6370326818228</v>
+        <v>791.4063498584283</v>
       </c>
       <c r="D31">
-        <v>1060.412032681823</v>
+        <v>1063.756349858428</v>
       </c>
       <c r="E31">
-        <v>-1.825000000000045</v>
+        <v>8.75</v>
       </c>
       <c r="F31">
-        <v>306.675</v>
+        <v>317.25</v>
       </c>
       <c r="G31">
         <v>44.9</v>
@@ -3835,28 +3835,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M31">
-        <v>17.725815</v>
+        <v>18.33705</v>
       </c>
       <c r="N31">
-        <v>58.55196277777777</v>
+        <v>57.94072777777777</v>
       </c>
       <c r="O31">
-        <v>14.63799069444444</v>
+        <v>14.48518194444444</v>
       </c>
       <c r="P31">
-        <v>43.91397208333333</v>
+        <v>43.45554583333332</v>
       </c>
       <c r="Q31">
-        <v>54.41397208333333</v>
+        <v>53.95554583333332</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1297614486754684</v>
+        <v>0.1307313537429555</v>
       </c>
       <c r="T31">
-        <v>1.221741382141801</v>
+        <v>1.23585468266712</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.303202858530216</v>
+        <v>4.159762763245874</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1045169476200689</v>
+        <v>0.1043317666805552</v>
       </c>
       <c r="C32">
-        <v>791.4063498584283</v>
+        <v>784.196828323405</v>
       </c>
       <c r="D32">
-        <v>1063.756349858428</v>
+        <v>1067.121828323405</v>
       </c>
       <c r="E32">
-        <v>8.75</v>
+        <v>19.32499999999999</v>
       </c>
       <c r="F32">
-        <v>317.25</v>
+        <v>327.825</v>
       </c>
       <c r="G32">
         <v>44.9</v>
@@ -3917,28 +3917,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M32">
-        <v>18.33705</v>
+        <v>18.948285</v>
       </c>
       <c r="N32">
-        <v>57.94072777777777</v>
+        <v>57.32949277777777</v>
       </c>
       <c r="O32">
-        <v>14.48518194444444</v>
+        <v>14.33237319444444</v>
       </c>
       <c r="P32">
-        <v>43.45554583333332</v>
+        <v>42.99711958333333</v>
       </c>
       <c r="Q32">
-        <v>53.95554583333332</v>
+        <v>53.49711958333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1307313537429555</v>
+        <v>0.1317293720008046</v>
       </c>
       <c r="T32">
-        <v>1.23585468266712</v>
+        <v>1.250377064367087</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.159762763245874</v>
+        <v>4.025576867657298</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1043317666805552</v>
+        <v>0.1049865857410415</v>
       </c>
       <c r="C33">
-        <v>784.196828323405</v>
+        <v>761.8155768848699</v>
       </c>
       <c r="D33">
-        <v>1067.121828323405</v>
+        <v>1055.31557688487</v>
       </c>
       <c r="E33">
-        <v>19.32499999999999</v>
+        <v>29.90000000000003</v>
       </c>
       <c r="F33">
-        <v>327.825</v>
+        <v>338.4</v>
       </c>
       <c r="G33">
         <v>44.9</v>
@@ -3999,45 +3999,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M33">
-        <v>18.948285</v>
+        <v>20.74392</v>
       </c>
       <c r="N33">
-        <v>57.32949277777777</v>
+        <v>55.53385777777777</v>
       </c>
       <c r="O33">
-        <v>14.33237319444444</v>
+        <v>13.88346444444444</v>
       </c>
       <c r="P33">
-        <v>42.99711958333333</v>
+        <v>41.65039333333333</v>
       </c>
       <c r="Q33">
-        <v>53.49711958333333</v>
+        <v>52.15039333333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1317293720008046</v>
+        <v>0.1327567437368257</v>
       </c>
       <c r="T33">
-        <v>1.250377064367087</v>
+        <v>1.265326574940581</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.025576867657298</v>
+        <v>3.677114922241204</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1049865857410415</v>
+        <v>0.1048276548015278</v>
       </c>
       <c r="C34">
-        <v>761.8155768848699</v>
+        <v>754.0819958211581</v>
       </c>
       <c r="D34">
-        <v>1055.31557688487</v>
+        <v>1058.156995821158</v>
       </c>
       <c r="E34">
-        <v>29.90000000000003</v>
+        <v>40.47500000000002</v>
       </c>
       <c r="F34">
-        <v>338.4</v>
+        <v>348.975</v>
       </c>
       <c r="G34">
         <v>44.9</v>
@@ -4081,28 +4081,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M34">
-        <v>20.74392</v>
+        <v>21.3921675</v>
       </c>
       <c r="N34">
-        <v>55.53385777777777</v>
+        <v>54.88561027777777</v>
       </c>
       <c r="O34">
-        <v>13.88346444444444</v>
+        <v>13.72140256944444</v>
       </c>
       <c r="P34">
-        <v>41.65039333333333</v>
+        <v>41.16420770833333</v>
       </c>
       <c r="Q34">
-        <v>52.15039333333333</v>
+        <v>51.66420770833333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1327567437368257</v>
+        <v>0.1338147832858624</v>
       </c>
       <c r="T34">
-        <v>1.265326574940581</v>
+        <v>1.280722339561046</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.677114922241204</v>
+        <v>3.565687197324804</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1048276548015278</v>
+        <v>0.1053827238620141</v>
       </c>
       <c r="C35">
-        <v>754.0819958211581</v>
+        <v>733.6492690935638</v>
       </c>
       <c r="D35">
-        <v>1058.156995821158</v>
+        <v>1048.299269093564</v>
       </c>
       <c r="E35">
-        <v>40.47500000000002</v>
+        <v>51.05000000000001</v>
       </c>
       <c r="F35">
-        <v>348.975</v>
+        <v>359.55</v>
       </c>
       <c r="G35">
         <v>44.9</v>
@@ -4163,45 +4163,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M35">
-        <v>21.3921675</v>
+        <v>23.047155</v>
       </c>
       <c r="N35">
-        <v>54.88561027777777</v>
+        <v>53.23062277777777</v>
       </c>
       <c r="O35">
-        <v>13.72140256944444</v>
+        <v>13.30765569444444</v>
       </c>
       <c r="P35">
-        <v>41.16420770833333</v>
+        <v>39.92296708333333</v>
       </c>
       <c r="Q35">
-        <v>51.66420770833333</v>
+        <v>50.42296708333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1338147832858624</v>
+        <v>0.1349048846394153</v>
       </c>
       <c r="T35">
-        <v>1.280722339561046</v>
+        <v>1.296584642503343</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.565687197324804</v>
+        <v>3.309639640024018</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1053827238620141</v>
+        <v>0.1052447929225004</v>
       </c>
       <c r="C36">
-        <v>733.6492690935638</v>
+        <v>725.5066588112991</v>
       </c>
       <c r="D36">
-        <v>1048.299269093564</v>
+        <v>1050.731658811299</v>
       </c>
       <c r="E36">
-        <v>51.05000000000001</v>
+        <v>61.62500000000006</v>
       </c>
       <c r="F36">
-        <v>359.55</v>
+        <v>370.1250000000001</v>
       </c>
       <c r="G36">
         <v>44.9</v>
@@ -4245,28 +4245,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M36">
-        <v>23.047155</v>
+        <v>23.72501250000001</v>
       </c>
       <c r="N36">
-        <v>53.23062277777777</v>
+        <v>52.55276527777777</v>
       </c>
       <c r="O36">
-        <v>13.30765569444444</v>
+        <v>13.13819131944444</v>
       </c>
       <c r="P36">
-        <v>39.92296708333333</v>
+        <v>39.41457395833332</v>
       </c>
       <c r="Q36">
-        <v>50.42296708333333</v>
+        <v>49.91457395833332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1349048846394153</v>
+        <v>0.1360285275730775</v>
       </c>
       <c r="T36">
-        <v>1.296584642503343</v>
+        <v>1.312935016305403</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.309639640024018</v>
+        <v>3.215078507451904</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1052447929225004</v>
+        <v>0.1051068619829867</v>
       </c>
       <c r="C37">
-        <v>725.5066588112991</v>
+        <v>717.3753626261835</v>
       </c>
       <c r="D37">
-        <v>1050.731658811299</v>
+        <v>1053.175362626183</v>
       </c>
       <c r="E37">
-        <v>61.62500000000006</v>
+        <v>72.20000000000005</v>
       </c>
       <c r="F37">
-        <v>370.1250000000001</v>
+        <v>380.7</v>
       </c>
       <c r="G37">
         <v>44.9</v>
@@ -4327,28 +4327,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M37">
-        <v>23.72501250000001</v>
+        <v>24.40287</v>
       </c>
       <c r="N37">
-        <v>52.55276527777777</v>
+        <v>51.87490777777776</v>
       </c>
       <c r="O37">
-        <v>13.13819131944444</v>
+        <v>12.96872694444444</v>
       </c>
       <c r="P37">
-        <v>39.41457395833332</v>
+        <v>38.90618083333332</v>
       </c>
       <c r="Q37">
-        <v>49.91457395833332</v>
+        <v>49.40618083333332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1360285275730775</v>
+        <v>0.1371872843484167</v>
       </c>
       <c r="T37">
-        <v>1.312935016305403</v>
+        <v>1.329796339288777</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.215078507451904</v>
+        <v>3.125770771133795</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1051068619829867</v>
+        <v>0.104968931043473</v>
       </c>
       <c r="C38">
-        <v>717.3753626261832</v>
+        <v>709.2554596623792</v>
       </c>
       <c r="D38">
-        <v>1053.175362626183</v>
+        <v>1055.630459662379</v>
       </c>
       <c r="E38">
-        <v>72.19999999999999</v>
+        <v>82.77499999999998</v>
       </c>
       <c r="F38">
-        <v>380.7</v>
+        <v>391.275</v>
       </c>
       <c r="G38">
         <v>44.9</v>
@@ -4409,28 +4409,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M38">
-        <v>24.40287</v>
+        <v>25.0807275</v>
       </c>
       <c r="N38">
-        <v>51.87490777777777</v>
+        <v>51.19705027777777</v>
       </c>
       <c r="O38">
-        <v>12.96872694444444</v>
+        <v>12.79926256944444</v>
       </c>
       <c r="P38">
-        <v>38.90618083333333</v>
+        <v>38.39778770833333</v>
       </c>
       <c r="Q38">
-        <v>49.40618083333333</v>
+        <v>48.89778770833333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1371872843484167</v>
+        <v>0.1383828270531317</v>
       </c>
       <c r="T38">
-        <v>1.329796339288777</v>
+        <v>1.347192942366861</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.125770771133796</v>
+        <v>3.041290480022071</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.104968931043473</v>
+        <v>0.1070540001039593</v>
       </c>
       <c r="C39">
-        <v>709.2554596623792</v>
+        <v>662.747093563621</v>
       </c>
       <c r="D39">
-        <v>1055.630459662379</v>
+        <v>1019.697093563621</v>
       </c>
       <c r="E39">
-        <v>82.77499999999998</v>
+        <v>93.35000000000002</v>
       </c>
       <c r="F39">
-        <v>391.275</v>
+        <v>401.85</v>
       </c>
       <c r="G39">
         <v>44.9</v>
@@ -4491,45 +4491,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M39">
-        <v>25.0807275</v>
+        <v>28.89301500000001</v>
       </c>
       <c r="N39">
-        <v>51.19705027777777</v>
+        <v>47.38476277777777</v>
       </c>
       <c r="O39">
-        <v>12.79926256944444</v>
+        <v>11.84619069444444</v>
       </c>
       <c r="P39">
-        <v>38.39778770833333</v>
+        <v>35.53857208333332</v>
       </c>
       <c r="Q39">
-        <v>48.89778770833333</v>
+        <v>46.03857208333332</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1383828270531317</v>
+        <v>0.1396169356515472</v>
       </c>
       <c r="T39">
-        <v>1.347192942366861</v>
+        <v>1.3651507261894</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.041290480022071</v>
+        <v>2.640007551229173</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1070540001039593</v>
+        <v>0.1069745691644456</v>
       </c>
       <c r="C40">
-        <v>662.747093563621</v>
+        <v>653.496099588795</v>
       </c>
       <c r="D40">
-        <v>1019.697093563621</v>
+        <v>1021.021099588795</v>
       </c>
       <c r="E40">
-        <v>93.35000000000002</v>
+        <v>103.925</v>
       </c>
       <c r="F40">
-        <v>401.85</v>
+        <v>412.425</v>
       </c>
       <c r="G40">
         <v>44.9</v>
@@ -4573,28 +4573,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M40">
-        <v>28.89301500000001</v>
+        <v>29.6533575</v>
       </c>
       <c r="N40">
-        <v>47.38476277777777</v>
+        <v>46.62442027777777</v>
       </c>
       <c r="O40">
-        <v>11.84619069444444</v>
+        <v>11.65610506944444</v>
       </c>
       <c r="P40">
-        <v>35.53857208333332</v>
+        <v>34.96831520833333</v>
       </c>
       <c r="Q40">
-        <v>46.03857208333332</v>
+        <v>45.46831520833333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1396169356515472</v>
+        <v>0.1408915068269599</v>
       </c>
       <c r="T40">
-        <v>1.3651507261894</v>
+        <v>1.383697289809399</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.640007551229173</v>
+        <v>2.572315049915605</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1069745691644456</v>
+        <v>0.1068951382249319</v>
       </c>
       <c r="C41">
-        <v>653.496099588795</v>
+        <v>644.2485483442922</v>
       </c>
       <c r="D41">
-        <v>1021.021099588795</v>
+        <v>1022.348548344292</v>
       </c>
       <c r="E41">
-        <v>103.925</v>
+        <v>114.5</v>
       </c>
       <c r="F41">
-        <v>412.425</v>
+        <v>423</v>
       </c>
       <c r="G41">
         <v>44.9</v>
@@ -4655,28 +4655,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M41">
-        <v>29.6533575</v>
+        <v>30.4137</v>
       </c>
       <c r="N41">
-        <v>46.62442027777777</v>
+        <v>45.86407777777777</v>
       </c>
       <c r="O41">
-        <v>11.65610506944444</v>
+        <v>11.46601944444444</v>
       </c>
       <c r="P41">
-        <v>34.96831520833333</v>
+        <v>34.39805833333332</v>
       </c>
       <c r="Q41">
-        <v>45.46831520833333</v>
+        <v>44.89805833333332</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1408915068269599</v>
+        <v>0.1422085637082198</v>
       </c>
       <c r="T41">
-        <v>1.383697289809399</v>
+        <v>1.402862072216731</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.572315049915605</v>
+        <v>2.508007173667714</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1068951382249319</v>
+        <v>0.1080149572854182</v>
       </c>
       <c r="C42">
-        <v>644.2485483442922</v>
+        <v>615.2720989043394</v>
       </c>
       <c r="D42">
-        <v>1022.348548344292</v>
+        <v>1003.947098904339</v>
       </c>
       <c r="E42">
-        <v>114.5</v>
+        <v>125.075</v>
       </c>
       <c r="F42">
-        <v>423</v>
+        <v>433.575</v>
       </c>
       <c r="G42">
         <v>44.9</v>
@@ -4737,45 +4737,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M42">
-        <v>30.4137</v>
+        <v>32.864985</v>
       </c>
       <c r="N42">
-        <v>45.86407777777777</v>
+        <v>43.41279277777777</v>
       </c>
       <c r="O42">
-        <v>11.46601944444444</v>
+        <v>10.85319819444444</v>
       </c>
       <c r="P42">
-        <v>34.39805833333332</v>
+        <v>32.55959458333332</v>
       </c>
       <c r="Q42">
-        <v>44.89805833333332</v>
+        <v>43.05959458333332</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1422085637082198</v>
+        <v>0.1435702665854545</v>
       </c>
       <c r="T42">
-        <v>1.402862072216731</v>
+        <v>1.42267650826499</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.508007173667714</v>
+        <v>2.320943635841543</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1080149572854182</v>
+        <v>0.1079647763459045</v>
       </c>
       <c r="C43">
-        <v>615.2720989043394</v>
+        <v>605.5075097447925</v>
       </c>
       <c r="D43">
-        <v>1003.947098904339</v>
+        <v>1004.757509744793</v>
       </c>
       <c r="E43">
-        <v>125.075</v>
+        <v>135.65</v>
       </c>
       <c r="F43">
-        <v>433.575</v>
+        <v>444.15</v>
       </c>
       <c r="G43">
         <v>44.9</v>
@@ -4819,28 +4819,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M43">
-        <v>32.864985</v>
+        <v>33.66657000000001</v>
       </c>
       <c r="N43">
-        <v>43.41279277777777</v>
+        <v>42.61120777777776</v>
       </c>
       <c r="O43">
-        <v>10.85319819444444</v>
+        <v>10.65280194444444</v>
       </c>
       <c r="P43">
-        <v>32.55959458333332</v>
+        <v>31.95840583333332</v>
       </c>
       <c r="Q43">
-        <v>43.05959458333332</v>
+        <v>42.45840583333332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1435702665854545</v>
+        <v>0.1449789247343181</v>
       </c>
       <c r="T43">
-        <v>1.42267650826499</v>
+        <v>1.443174200728706</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.320943635841543</v>
+        <v>2.265683073083411</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1079647763459045</v>
+        <v>0.1079145954063908</v>
       </c>
       <c r="C44">
-        <v>605.5075097447926</v>
+        <v>595.7442300094515</v>
       </c>
       <c r="D44">
-        <v>1004.757509744793</v>
+        <v>1005.569230009451</v>
       </c>
       <c r="E44">
-        <v>135.65</v>
+        <v>146.225</v>
       </c>
       <c r="F44">
-        <v>444.15</v>
+        <v>454.725</v>
       </c>
       <c r="G44">
         <v>44.9</v>
@@ -4901,28 +4901,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M44">
-        <v>33.66657</v>
+        <v>34.468155</v>
       </c>
       <c r="N44">
-        <v>42.61120777777777</v>
+        <v>41.80962277777777</v>
       </c>
       <c r="O44">
-        <v>10.65280194444444</v>
+        <v>10.45240569444444</v>
       </c>
       <c r="P44">
-        <v>31.95840583333333</v>
+        <v>31.35721708333332</v>
       </c>
       <c r="Q44">
-        <v>42.45840583333333</v>
+        <v>41.85721708333332</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1449789247343181</v>
+        <v>0.1464370094848961</v>
       </c>
       <c r="T44">
-        <v>1.443174200728706</v>
+        <v>1.464391110471851</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.265683073083411</v>
+        <v>2.212992769058215</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1079145954063908</v>
+        <v>0.1078644144668771</v>
       </c>
       <c r="C45">
-        <v>595.7442300094515</v>
+        <v>585.9822628744416</v>
       </c>
       <c r="D45">
-        <v>1005.569230009451</v>
+        <v>1006.382262874442</v>
       </c>
       <c r="E45">
-        <v>146.225</v>
+        <v>156.8</v>
       </c>
       <c r="F45">
-        <v>454.725</v>
+        <v>465.3</v>
       </c>
       <c r="G45">
         <v>44.9</v>
@@ -4983,28 +4983,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M45">
-        <v>34.468155</v>
+        <v>35.26974000000001</v>
       </c>
       <c r="N45">
-        <v>41.80962277777777</v>
+        <v>41.00803777777777</v>
       </c>
       <c r="O45">
-        <v>10.45240569444444</v>
+        <v>10.25200944444444</v>
       </c>
       <c r="P45">
-        <v>31.35721708333332</v>
+        <v>30.75602833333333</v>
       </c>
       <c r="Q45">
-        <v>41.85721708333332</v>
+        <v>41.25602833333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1464370094848961</v>
+        <v>0.1479471686908519</v>
       </c>
       <c r="T45">
-        <v>1.464391110471851</v>
+        <v>1.486365766991537</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.212992769058215</v>
+        <v>2.162697478852347</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1078644144668771</v>
+        <v>0.1078142335273634</v>
       </c>
       <c r="C46">
-        <v>585.9822628744416</v>
+        <v>576.2216115261701</v>
       </c>
       <c r="D46">
-        <v>1006.382262874442</v>
+        <v>1007.19661152617</v>
       </c>
       <c r="E46">
-        <v>156.8</v>
+        <v>167.375</v>
       </c>
       <c r="F46">
-        <v>465.3</v>
+        <v>475.875</v>
       </c>
       <c r="G46">
         <v>44.9</v>
@@ -5065,28 +5065,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M46">
-        <v>35.26974000000001</v>
+        <v>36.071325</v>
       </c>
       <c r="N46">
-        <v>41.00803777777777</v>
+        <v>40.20645277777777</v>
       </c>
       <c r="O46">
-        <v>10.25200944444444</v>
+        <v>10.05161319444444</v>
       </c>
       <c r="P46">
-        <v>30.75602833333333</v>
+        <v>30.15483958333333</v>
       </c>
       <c r="Q46">
-        <v>41.25602833333333</v>
+        <v>40.65483958333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1479471686908519</v>
+        <v>0.1495122427770243</v>
       </c>
       <c r="T46">
-        <v>1.486365766991537</v>
+        <v>1.50913950193012</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.162697478852347</v>
+        <v>2.11463753487785</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1078142335273634</v>
+        <v>0.1077640525878497</v>
       </c>
       <c r="C47">
-        <v>576.2216115261701</v>
+        <v>566.4622791613642</v>
       </c>
       <c r="D47">
-        <v>1007.19661152617</v>
+        <v>1008.012279161364</v>
       </c>
       <c r="E47">
-        <v>167.375</v>
+        <v>177.95</v>
       </c>
       <c r="F47">
-        <v>475.875</v>
+        <v>486.45</v>
       </c>
       <c r="G47">
         <v>44.9</v>
@@ -5147,28 +5147,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M47">
-        <v>36.071325</v>
+        <v>36.87291</v>
       </c>
       <c r="N47">
-        <v>40.20645277777777</v>
+        <v>39.40486777777777</v>
       </c>
       <c r="O47">
-        <v>10.05161319444444</v>
+        <v>9.851216944444442</v>
       </c>
       <c r="P47">
-        <v>30.15483958333333</v>
+        <v>29.55365083333333</v>
       </c>
       <c r="Q47">
-        <v>40.65483958333333</v>
+        <v>40.05365083333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1495122427770243</v>
+        <v>0.151135282570092</v>
       </c>
       <c r="T47">
-        <v>1.50913950193012</v>
+        <v>1.532756708533095</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.11463753487785</v>
+        <v>2.068667153684853</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1077640525878497</v>
+        <v>0.107713871648336</v>
       </c>
       <c r="C48">
-        <v>566.4622791613642</v>
+        <v>556.7042689871171</v>
       </c>
       <c r="D48">
-        <v>1008.012279161364</v>
+        <v>1008.829268987117</v>
       </c>
       <c r="E48">
-        <v>177.95</v>
+        <v>188.525</v>
       </c>
       <c r="F48">
-        <v>486.45</v>
+        <v>497.025</v>
       </c>
       <c r="G48">
         <v>44.9</v>
@@ -5229,28 +5229,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M48">
-        <v>36.87291</v>
+        <v>37.67449500000001</v>
       </c>
       <c r="N48">
-        <v>39.40486777777777</v>
+        <v>38.60328277777776</v>
       </c>
       <c r="O48">
-        <v>9.851216944444442</v>
+        <v>9.650820694444441</v>
       </c>
       <c r="P48">
-        <v>29.55365083333333</v>
+        <v>28.95246208333332</v>
       </c>
       <c r="Q48">
-        <v>40.05365083333332</v>
+        <v>39.45246208333332</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.151135282570092</v>
+        <v>0.1528195691478037</v>
       </c>
       <c r="T48">
-        <v>1.532756708533095</v>
+        <v>1.557265130479579</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.068667153684853</v>
+        <v>2.024652958925601</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.107713871648336</v>
+        <v>0.1127756907088223</v>
       </c>
       <c r="C49">
-        <v>556.7042689871171</v>
+        <v>469.8850202381778</v>
       </c>
       <c r="D49">
-        <v>1008.829268987117</v>
+        <v>932.5850202381779</v>
       </c>
       <c r="E49">
-        <v>188.525</v>
+        <v>199.1</v>
       </c>
       <c r="F49">
-        <v>497.025</v>
+        <v>507.6</v>
       </c>
       <c r="G49">
         <v>44.9</v>
@@ -5311,45 +5311,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M49">
-        <v>37.67449500000001</v>
+        <v>45.684</v>
       </c>
       <c r="N49">
-        <v>38.60328277777776</v>
+        <v>30.59377777777777</v>
       </c>
       <c r="O49">
-        <v>9.650820694444441</v>
+        <v>7.648444444444443</v>
       </c>
       <c r="P49">
-        <v>28.95246208333332</v>
+        <v>22.94533333333333</v>
       </c>
       <c r="Q49">
-        <v>39.45246208333332</v>
+        <v>33.44533333333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1528195691478037</v>
+        <v>0.1545686359785044</v>
       </c>
       <c r="T49">
-        <v>1.557265130479579</v>
+        <v>1.582716184039389</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.024652958925601</v>
+        <v>1.669682553580636</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1127756907088223</v>
+        <v>0.1128320097693086</v>
       </c>
       <c r="C50">
-        <v>469.8850202381781</v>
+        <v>458.5264794739348</v>
       </c>
       <c r="D50">
-        <v>932.5850202381781</v>
+        <v>931.8014794739348</v>
       </c>
       <c r="E50">
-        <v>199.1</v>
+        <v>209.675</v>
       </c>
       <c r="F50">
-        <v>507.6</v>
+        <v>518.175</v>
       </c>
       <c r="G50">
         <v>44.9</v>
@@ -5393,28 +5393,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M50">
-        <v>45.684</v>
+        <v>46.63574999999999</v>
       </c>
       <c r="N50">
-        <v>30.59377777777777</v>
+        <v>29.64202777777778</v>
       </c>
       <c r="O50">
-        <v>7.648444444444443</v>
+        <v>7.410506944444444</v>
       </c>
       <c r="P50">
-        <v>22.94533333333333</v>
+        <v>22.23152083333333</v>
       </c>
       <c r="Q50">
-        <v>33.44533333333333</v>
+        <v>32.73152083333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1545686359785044</v>
+        <v>0.1563862936653109</v>
       </c>
       <c r="T50">
-        <v>1.582716184039389</v>
+        <v>1.609165318130956</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.669682553580636</v>
+        <v>1.635607399425929</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1128320097693086</v>
+        <v>0.1128883288297949</v>
       </c>
       <c r="C51">
-        <v>458.5264794739348</v>
+        <v>447.1692542374581</v>
       </c>
       <c r="D51">
-        <v>931.8014794739348</v>
+        <v>931.0192542374581</v>
       </c>
       <c r="E51">
-        <v>209.675</v>
+        <v>220.25</v>
       </c>
       <c r="F51">
-        <v>518.175</v>
+        <v>528.75</v>
       </c>
       <c r="G51">
         <v>44.9</v>
@@ -5475,28 +5475,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M51">
-        <v>46.63574999999999</v>
+        <v>47.5875</v>
       </c>
       <c r="N51">
-        <v>29.64202777777778</v>
+        <v>28.69027777777777</v>
       </c>
       <c r="O51">
-        <v>7.410506944444444</v>
+        <v>7.172569444444443</v>
       </c>
       <c r="P51">
-        <v>22.23152083333333</v>
+        <v>21.51770833333333</v>
       </c>
       <c r="Q51">
-        <v>32.73152083333333</v>
+        <v>32.01770833333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1563862936653109</v>
+        <v>0.1582766576595898</v>
       </c>
       <c r="T51">
-        <v>1.609165318130956</v>
+        <v>1.636672417586186</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.635607399425929</v>
+        <v>1.602895251437411</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1128883288297949</v>
+        <v>0.1129446478902812</v>
       </c>
       <c r="C52">
-        <v>447.1692542374581</v>
+        <v>435.8133412184635</v>
       </c>
       <c r="D52">
-        <v>931.0192542374581</v>
+        <v>930.2383412184636</v>
       </c>
       <c r="E52">
-        <v>220.25</v>
+        <v>230.825</v>
       </c>
       <c r="F52">
-        <v>528.75</v>
+        <v>539.325</v>
       </c>
       <c r="G52">
         <v>44.9</v>
@@ -5557,28 +5557,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M52">
-        <v>47.5875</v>
+        <v>48.53925</v>
       </c>
       <c r="N52">
-        <v>28.69027777777777</v>
+        <v>27.73852777777777</v>
       </c>
       <c r="O52">
-        <v>7.172569444444443</v>
+        <v>6.934631944444442</v>
       </c>
       <c r="P52">
-        <v>21.51770833333333</v>
+        <v>20.80389583333333</v>
       </c>
       <c r="Q52">
-        <v>32.01770833333333</v>
+        <v>31.30389583333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1582766576595898</v>
+        <v>0.1602441793679208</v>
       </c>
       <c r="T52">
-        <v>1.636672417586186</v>
+        <v>1.665302255794691</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.602895251437411</v>
+        <v>1.571465932781775</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1129446478902812</v>
+        <v>0.1130009669507675</v>
       </c>
       <c r="C53">
-        <v>435.8133412184635</v>
+        <v>424.4587371177646</v>
       </c>
       <c r="D53">
-        <v>930.2383412184636</v>
+        <v>929.4587371177646</v>
       </c>
       <c r="E53">
-        <v>230.825</v>
+        <v>241.4</v>
       </c>
       <c r="F53">
-        <v>539.325</v>
+        <v>549.9</v>
       </c>
       <c r="G53">
         <v>44.9</v>
@@ -5639,28 +5639,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M53">
-        <v>48.53925</v>
+        <v>49.491</v>
       </c>
       <c r="N53">
-        <v>27.73852777777777</v>
+        <v>26.78677777777777</v>
       </c>
       <c r="O53">
-        <v>6.934631944444442</v>
+        <v>6.696694444444443</v>
       </c>
       <c r="P53">
-        <v>20.80389583333333</v>
+        <v>20.09008333333333</v>
       </c>
       <c r="Q53">
-        <v>31.30389583333333</v>
+        <v>30.59008333333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1602441793679208</v>
+        <v>0.1622936811474323</v>
       </c>
       <c r="T53">
-        <v>1.665302255794691</v>
+        <v>1.69512500392855</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.571465932781775</v>
+        <v>1.541245434074433</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1130009669507675</v>
+        <v>0.1130572860112538</v>
       </c>
       <c r="C54">
-        <v>424.4587371177646</v>
+        <v>413.1054386472244</v>
       </c>
       <c r="D54">
-        <v>929.4587371177646</v>
+        <v>928.6804386472245</v>
       </c>
       <c r="E54">
-        <v>241.4</v>
+        <v>251.975</v>
       </c>
       <c r="F54">
-        <v>549.9</v>
+        <v>560.475</v>
       </c>
       <c r="G54">
         <v>44.9</v>
@@ -5721,28 +5721,28 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M54">
-        <v>49.491</v>
+        <v>50.44275</v>
       </c>
       <c r="N54">
-        <v>26.78677777777777</v>
+        <v>25.83502777777777</v>
       </c>
       <c r="O54">
-        <v>6.696694444444443</v>
+        <v>6.458756944444444</v>
       </c>
       <c r="P54">
-        <v>20.09008333333333</v>
+        <v>19.37627083333333</v>
       </c>
       <c r="Q54">
-        <v>30.59008333333333</v>
+        <v>29.87627083333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1622936811474323</v>
+        <v>0.1644303957686251</v>
       </c>
       <c r="T54">
-        <v>1.69512500392855</v>
+        <v>1.726216805174489</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.541245434074433</v>
+        <v>1.512165331544727</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1130572860112538</v>
+        <v>0.1386847346270573</v>
       </c>
       <c r="C55">
-        <v>413.1054386472244</v>
+        <v>146.3020032913809</v>
       </c>
       <c r="D55">
-        <v>928.6804386472245</v>
+        <v>672.4520032913809</v>
       </c>
       <c r="E55">
-        <v>251.975</v>
+        <v>262.5500000000001</v>
       </c>
       <c r="F55">
-        <v>560.475</v>
+        <v>571.0500000000001</v>
       </c>
       <c r="G55">
         <v>44.9</v>
@@ -5803,45 +5803,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M55">
-        <v>50.44275</v>
+        <v>83.83014000000001</v>
       </c>
       <c r="N55">
-        <v>25.83502777777777</v>
+        <v>-7.552362222222243</v>
       </c>
       <c r="O55">
-        <v>6.458756944444444</v>
+        <v>-1.888090555555561</v>
       </c>
       <c r="P55">
-        <v>19.37627083333333</v>
+        <v>-5.664271666666682</v>
       </c>
       <c r="Q55">
-        <v>29.87627083333333</v>
+        <v>4.835728333333318</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1644303957686251</v>
+        <v>0.1683593613168004</v>
       </c>
       <c r="T55">
-        <v>1.726216805174489</v>
+        <v>1.783388041199359</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.25</v>
+        <v>0.2274771871363264</v>
       </c>
       <c r="W55">
-        <v>0.0675</v>
+        <v>0.1134063489283873</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.512165331544727</v>
+        <v>0.9099087485453056</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1386847346270573</v>
+        <v>0.1396947346270573</v>
       </c>
       <c r="C56">
-        <v>146.3020032913809</v>
+        <v>128.4936208656045</v>
       </c>
       <c r="D56">
-        <v>672.4520032913809</v>
+        <v>665.2186208656045</v>
       </c>
       <c r="E56">
-        <v>262.5500000000001</v>
+        <v>273.125</v>
       </c>
       <c r="F56">
-        <v>571.0500000000001</v>
+        <v>581.625</v>
       </c>
       <c r="G56">
         <v>44.9</v>
@@ -5885,37 +5885,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M56">
-        <v>83.83014000000001</v>
+        <v>85.38255000000001</v>
       </c>
       <c r="N56">
-        <v>-7.552362222222243</v>
+        <v>-9.104772222222238</v>
       </c>
       <c r="O56">
-        <v>-1.888090555555561</v>
+        <v>-2.276193055555559</v>
       </c>
       <c r="P56">
-        <v>-5.664271666666682</v>
+        <v>-6.828579166666678</v>
       </c>
       <c r="Q56">
-        <v>4.835728333333318</v>
+        <v>3.671420833333322</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1683593613168004</v>
+        <v>0.1710829026793959</v>
       </c>
       <c r="T56">
-        <v>1.783388041199359</v>
+        <v>1.823018886559344</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2274771871363264</v>
+        <v>0.2233412382793023</v>
       </c>
       <c r="W56">
-        <v>0.1134063489283873</v>
+        <v>0.1140135062205984</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9099087485453056</v>
+        <v>0.8933649531172091</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1396947346270573</v>
+        <v>0.1407047346270573</v>
       </c>
       <c r="C57">
-        <v>128.4936208656045</v>
+        <v>110.8391973814709</v>
       </c>
       <c r="D57">
-        <v>665.2186208656045</v>
+        <v>658.1391973814709</v>
       </c>
       <c r="E57">
-        <v>273.125</v>
+        <v>283.7</v>
       </c>
       <c r="F57">
-        <v>581.625</v>
+        <v>592.2</v>
       </c>
       <c r="G57">
         <v>44.9</v>
@@ -5967,37 +5967,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M57">
-        <v>85.38255000000001</v>
+        <v>86.93496000000002</v>
       </c>
       <c r="N57">
-        <v>-9.104772222222238</v>
+        <v>-10.65718222222225</v>
       </c>
       <c r="O57">
-        <v>-2.276193055555559</v>
+        <v>-2.664295555555562</v>
       </c>
       <c r="P57">
-        <v>-6.828579166666678</v>
+        <v>-7.992886666666685</v>
       </c>
       <c r="Q57">
-        <v>3.671420833333322</v>
+        <v>2.507113333333315</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1710829026793959</v>
+        <v>0.1739302413766549</v>
       </c>
       <c r="T57">
-        <v>1.823018886559344</v>
+        <v>1.864451133981148</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2233412382793023</v>
+        <v>0.2193530018814576</v>
       </c>
       <c r="W57">
-        <v>0.1140135062205984</v>
+        <v>0.114598979323802</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8933649531172091</v>
+        <v>0.8774120075258303</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1407047346270573</v>
+        <v>0.1417147346270573</v>
       </c>
       <c r="C58">
-        <v>110.8391973814709</v>
+        <v>93.33386919008387</v>
       </c>
       <c r="D58">
-        <v>658.1391973814709</v>
+        <v>651.208869190084</v>
       </c>
       <c r="E58">
-        <v>283.7</v>
+        <v>294.2750000000001</v>
       </c>
       <c r="F58">
-        <v>592.2</v>
+        <v>602.7750000000001</v>
       </c>
       <c r="G58">
         <v>44.9</v>
@@ -6049,37 +6049,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M58">
-        <v>86.93496000000002</v>
+        <v>88.48737000000003</v>
       </c>
       <c r="N58">
-        <v>-10.65718222222225</v>
+        <v>-12.20959222222226</v>
       </c>
       <c r="O58">
-        <v>-2.664295555555562</v>
+        <v>-3.052398055555564</v>
       </c>
       <c r="P58">
-        <v>-7.992886666666685</v>
+        <v>-9.157194166666692</v>
       </c>
       <c r="Q58">
-        <v>2.507113333333315</v>
+        <v>1.342805833333308</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1739302413766549</v>
+        <v>0.176910014431926</v>
       </c>
       <c r="T58">
-        <v>1.864451133981148</v>
+        <v>1.907810462678384</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2193530018814576</v>
+        <v>0.2155047036028355</v>
       </c>
       <c r="W58">
-        <v>0.114598979323802</v>
+        <v>0.1151639095111038</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8774120075258303</v>
+        <v>0.862018814411342</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1417147346270573</v>
+        <v>0.1427247346270573</v>
       </c>
       <c r="C59">
-        <v>93.33386919008387</v>
+        <v>75.97297536831866</v>
       </c>
       <c r="D59">
-        <v>651.208869190084</v>
+        <v>644.4229753683187</v>
       </c>
       <c r="E59">
-        <v>294.2750000000001</v>
+        <v>304.85</v>
       </c>
       <c r="F59">
-        <v>602.7750000000001</v>
+        <v>613.35</v>
       </c>
       <c r="G59">
         <v>44.9</v>
@@ -6131,37 +6131,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M59">
-        <v>88.48737000000003</v>
+        <v>90.03978000000001</v>
       </c>
       <c r="N59">
-        <v>-12.20959222222226</v>
+        <v>-13.76200222222224</v>
       </c>
       <c r="O59">
-        <v>-3.052398055555564</v>
+        <v>-3.440500555555559</v>
       </c>
       <c r="P59">
-        <v>-9.157194166666692</v>
+        <v>-10.32150166666668</v>
       </c>
       <c r="Q59">
-        <v>1.342805833333308</v>
+        <v>0.178498333333323</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.176910014431926</v>
+        <v>0.18003168144221</v>
       </c>
       <c r="T59">
-        <v>1.907810462678384</v>
+        <v>1.953234521313584</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2155047036028355</v>
+        <v>0.2117891052648556</v>
       </c>
       <c r="W59">
-        <v>0.1151639095111038</v>
+        <v>0.1157093593471192</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.862018814411342</v>
+        <v>0.8471564210594225</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1427247346270573</v>
+        <v>0.1437347346270573</v>
       </c>
       <c r="C60">
-        <v>75.97297536831877</v>
+        <v>58.75204726527602</v>
       </c>
       <c r="D60">
-        <v>644.4229753683187</v>
+        <v>637.777047265276</v>
       </c>
       <c r="E60">
-        <v>304.8499999999999</v>
+        <v>315.425</v>
       </c>
       <c r="F60">
-        <v>613.3499999999999</v>
+        <v>623.925</v>
       </c>
       <c r="G60">
         <v>44.9</v>
@@ -6213,37 +6213,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M60">
-        <v>90.03977999999999</v>
+        <v>91.59219</v>
       </c>
       <c r="N60">
-        <v>-13.76200222222222</v>
+        <v>-15.31441222222223</v>
       </c>
       <c r="O60">
-        <v>-3.440500555555555</v>
+        <v>-3.828603055555558</v>
       </c>
       <c r="P60">
-        <v>-10.32150166666667</v>
+        <v>-11.48580916666667</v>
       </c>
       <c r="Q60">
-        <v>0.1784983333333336</v>
+        <v>-0.9858091666666731</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1800316814422099</v>
+        <v>0.1833056248920199</v>
       </c>
       <c r="T60">
-        <v>1.953234521313583</v>
+        <v>2.000874387687085</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2117891052648556</v>
+        <v>0.2081994594129089</v>
       </c>
       <c r="W60">
-        <v>0.1157093593471192</v>
+        <v>0.116236319358185</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8471564210594226</v>
+        <v>0.8327978376516356</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1437347346270573</v>
+        <v>0.1447447346270573</v>
       </c>
       <c r="C61">
-        <v>58.75204726527602</v>
+        <v>41.6667986889787</v>
       </c>
       <c r="D61">
-        <v>637.777047265276</v>
+        <v>631.2667986889787</v>
       </c>
       <c r="E61">
-        <v>315.425</v>
+        <v>326</v>
       </c>
       <c r="F61">
-        <v>623.925</v>
+        <v>634.5</v>
       </c>
       <c r="G61">
         <v>44.9</v>
@@ -6295,37 +6295,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M61">
-        <v>91.59219</v>
+        <v>93.14460000000001</v>
       </c>
       <c r="N61">
-        <v>-15.31441222222223</v>
+        <v>-16.86682222222224</v>
       </c>
       <c r="O61">
-        <v>-3.828603055555558</v>
+        <v>-4.21670555555556</v>
       </c>
       <c r="P61">
-        <v>-11.48580916666667</v>
+        <v>-12.65011666666668</v>
       </c>
       <c r="Q61">
-        <v>-0.9858091666666731</v>
+        <v>-2.15011666666668</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1833056248920199</v>
+        <v>0.1867432655143204</v>
       </c>
       <c r="T61">
-        <v>2.000874387687085</v>
+        <v>2.050896247379262</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2081994594129089</v>
+        <v>0.2047294684226938</v>
       </c>
       <c r="W61">
-        <v>0.116236319358185</v>
+        <v>0.1167457140355486</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8327978376516356</v>
+        <v>0.818917873690775</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1447447346270573</v>
+        <v>0.1457547346270573</v>
       </c>
       <c r="C62">
-        <v>41.6667986889787</v>
+        <v>24.71311668802321</v>
       </c>
       <c r="D62">
-        <v>631.2667986889787</v>
+        <v>624.8881166880232</v>
       </c>
       <c r="E62">
-        <v>326</v>
+        <v>336.5749999999999</v>
       </c>
       <c r="F62">
-        <v>634.5</v>
+        <v>645.0749999999999</v>
       </c>
       <c r="G62">
         <v>44.9</v>
@@ -6377,37 +6377,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M62">
-        <v>93.14460000000001</v>
+        <v>94.69701000000001</v>
       </c>
       <c r="N62">
-        <v>-16.86682222222224</v>
+        <v>-18.41923222222223</v>
       </c>
       <c r="O62">
-        <v>-4.21670555555556</v>
+        <v>-4.604808055555559</v>
       </c>
       <c r="P62">
-        <v>-12.65011666666668</v>
+        <v>-13.81442416666668</v>
       </c>
       <c r="Q62">
-        <v>-2.15011666666668</v>
+        <v>-3.314424166666676</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1867432655143204</v>
+        <v>0.190357195399303</v>
       </c>
       <c r="T62">
-        <v>2.050896247379262</v>
+        <v>2.103483330645397</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2047294684226938</v>
+        <v>0.2013732476288791</v>
       </c>
       <c r="W62">
-        <v>0.1167457140355486</v>
+        <v>0.1172384072480806</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.818917873690775</v>
+        <v>0.8054929905155165</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1457547346270573</v>
+        <v>0.1823679107146399</v>
       </c>
       <c r="C63">
-        <v>24.71311668802321</v>
+        <v>-153.3912724020879</v>
       </c>
       <c r="D63">
-        <v>624.8881166880232</v>
+        <v>457.3587275979121</v>
       </c>
       <c r="E63">
-        <v>336.5749999999999</v>
+        <v>347.15</v>
       </c>
       <c r="F63">
-        <v>645.0749999999999</v>
+        <v>655.65</v>
       </c>
       <c r="G63">
         <v>44.9</v>
@@ -6459,45 +6459,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M63">
-        <v>94.69701000000001</v>
+        <v>131.65452</v>
       </c>
       <c r="N63">
-        <v>-18.41923222222223</v>
+        <v>-55.37674222222222</v>
       </c>
       <c r="O63">
-        <v>-4.604808055555559</v>
+        <v>-13.84418555555555</v>
       </c>
       <c r="P63">
-        <v>-13.81442416666668</v>
+        <v>-41.53255666666666</v>
       </c>
       <c r="Q63">
-        <v>-3.314424166666676</v>
+        <v>-31.03255666666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.190357195399303</v>
+        <v>0.1997486376139758</v>
       </c>
       <c r="T63">
-        <v>2.103483330645397</v>
+        <v>2.240140257993193</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.2013732476288791</v>
+        <v>0.1448445860001194</v>
       </c>
       <c r="W63">
-        <v>0.1172384072480806</v>
+        <v>0.171715207131176</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8054929905155165</v>
+        <v>0.5793783440004777</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1823679107146399</v>
+        <v>0.1839179107146399</v>
       </c>
       <c r="C64">
-        <v>-153.3912724020879</v>
+        <v>-169.0988871665945</v>
       </c>
       <c r="D64">
-        <v>457.3587275979121</v>
+        <v>452.2261128334055</v>
       </c>
       <c r="E64">
-        <v>347.15</v>
+        <v>357.725</v>
       </c>
       <c r="F64">
-        <v>655.65</v>
+        <v>666.225</v>
       </c>
       <c r="G64">
         <v>44.9</v>
@@ -6541,37 +6541,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M64">
-        <v>131.65452</v>
+        <v>133.77798</v>
       </c>
       <c r="N64">
-        <v>-55.37674222222222</v>
+        <v>-57.50020222222224</v>
       </c>
       <c r="O64">
-        <v>-13.84418555555555</v>
+        <v>-14.37505055555556</v>
       </c>
       <c r="P64">
-        <v>-41.53255666666666</v>
+        <v>-43.12515166666668</v>
       </c>
       <c r="Q64">
-        <v>-31.03255666666666</v>
+        <v>-32.62515166666668</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1997486376139758</v>
+        <v>0.2039094116035427</v>
       </c>
       <c r="T64">
-        <v>2.240140257993193</v>
+        <v>2.300684589290306</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1448445860001194</v>
+        <v>0.1425454655874191</v>
       </c>
       <c r="W64">
-        <v>0.171715207131176</v>
+        <v>0.1721768705100462</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5793783440004777</v>
+        <v>0.5701818623496764</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1839179107146399</v>
+        <v>0.1854679107146399</v>
       </c>
       <c r="C65">
-        <v>-169.0988871665945</v>
+        <v>-184.6925809474724</v>
       </c>
       <c r="D65">
-        <v>452.2261128334055</v>
+        <v>447.2074190525277</v>
       </c>
       <c r="E65">
-        <v>357.725</v>
+        <v>368.3000000000001</v>
       </c>
       <c r="F65">
-        <v>666.225</v>
+        <v>676.8000000000001</v>
       </c>
       <c r="G65">
         <v>44.9</v>
@@ -6623,37 +6623,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M65">
-        <v>133.77798</v>
+        <v>135.90144</v>
       </c>
       <c r="N65">
-        <v>-57.50020222222224</v>
+        <v>-59.62366222222224</v>
       </c>
       <c r="O65">
-        <v>-14.37505055555556</v>
+        <v>-14.90591555555556</v>
       </c>
       <c r="P65">
-        <v>-43.12515166666668</v>
+        <v>-44.71774666666668</v>
       </c>
       <c r="Q65">
-        <v>-32.62515166666668</v>
+        <v>-34.21774666666668</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2039094116035427</v>
+        <v>0.2083013397036411</v>
       </c>
       <c r="T65">
-        <v>2.300684589290306</v>
+        <v>2.36459249454837</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1425454655874191</v>
+        <v>0.1403181926876157</v>
       </c>
       <c r="W65">
-        <v>0.1721768705100462</v>
+        <v>0.1726241069083268</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5701818623496764</v>
+        <v>0.5612727707504628</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1854679107146399</v>
+        <v>0.1870179107146399</v>
       </c>
       <c r="C66">
-        <v>-184.6925809474724</v>
+        <v>-200.1761049160228</v>
       </c>
       <c r="D66">
-        <v>447.2074190525277</v>
+        <v>442.2988950839772</v>
       </c>
       <c r="E66">
-        <v>368.3000000000001</v>
+        <v>378.875</v>
       </c>
       <c r="F66">
-        <v>676.8000000000001</v>
+        <v>687.375</v>
       </c>
       <c r="G66">
         <v>44.9</v>
@@ -6705,37 +6705,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M66">
-        <v>135.90144</v>
+        <v>138.0249</v>
       </c>
       <c r="N66">
-        <v>-59.62366222222224</v>
+        <v>-61.74712222222223</v>
       </c>
       <c r="O66">
-        <v>-14.90591555555556</v>
+        <v>-15.43678055555556</v>
       </c>
       <c r="P66">
-        <v>-44.71774666666668</v>
+        <v>-46.31034166666667</v>
       </c>
       <c r="Q66">
-        <v>-34.21774666666668</v>
+        <v>-35.81034166666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2083013397036411</v>
+        <v>0.2129442351237451</v>
       </c>
       <c r="T66">
-        <v>2.36459249454837</v>
+        <v>2.432152280106895</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1403181926876157</v>
+        <v>0.1381594512616524</v>
       </c>
       <c r="W66">
-        <v>0.1726241069083268</v>
+        <v>0.1730575821866602</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5612727707504628</v>
+        <v>0.5526378050466094</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1870179107146399</v>
+        <v>0.1885679107146399</v>
       </c>
       <c r="C67">
-        <v>-200.1761049160228</v>
+        <v>-215.5530473409593</v>
       </c>
       <c r="D67">
-        <v>442.2988950839772</v>
+        <v>437.4969526590408</v>
       </c>
       <c r="E67">
-        <v>378.875</v>
+        <v>389.45</v>
       </c>
       <c r="F67">
-        <v>687.375</v>
+        <v>697.95</v>
       </c>
       <c r="G67">
         <v>44.9</v>
@@ -6787,37 +6787,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M67">
-        <v>138.0249</v>
+        <v>140.14836</v>
       </c>
       <c r="N67">
-        <v>-61.74712222222223</v>
+        <v>-63.87058222222225</v>
       </c>
       <c r="O67">
-        <v>-15.43678055555556</v>
+        <v>-15.96764555555556</v>
       </c>
       <c r="P67">
-        <v>-46.31034166666667</v>
+        <v>-47.90293666666669</v>
       </c>
       <c r="Q67">
-        <v>-35.81034166666667</v>
+        <v>-37.40293666666669</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2129442351237451</v>
+        <v>0.2178602420391494</v>
       </c>
       <c r="T67">
-        <v>2.432152280106895</v>
+        <v>2.503686170698275</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1381594512616524</v>
+        <v>0.1360661262425364</v>
       </c>
       <c r="W67">
-        <v>0.1730575821866602</v>
+        <v>0.1734779218504987</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5526378050466094</v>
+        <v>0.5442645049701456</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1885679107146399</v>
+        <v>0.1901179107146399</v>
       </c>
       <c r="C68">
-        <v>-215.5530473409593</v>
+        <v>-230.8268423364215</v>
       </c>
       <c r="D68">
-        <v>437.4969526590408</v>
+        <v>432.7981576635786</v>
       </c>
       <c r="E68">
-        <v>389.45</v>
+        <v>400.0250000000001</v>
       </c>
       <c r="F68">
-        <v>697.95</v>
+        <v>708.5250000000001</v>
       </c>
       <c r="G68">
         <v>44.9</v>
@@ -6869,37 +6869,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M68">
-        <v>140.14836</v>
+        <v>142.27182</v>
       </c>
       <c r="N68">
-        <v>-63.87058222222225</v>
+        <v>-65.99404222222225</v>
       </c>
       <c r="O68">
-        <v>-15.96764555555556</v>
+        <v>-16.49851055555556</v>
       </c>
       <c r="P68">
-        <v>-47.90293666666669</v>
+        <v>-49.49553166666669</v>
       </c>
       <c r="Q68">
-        <v>-37.40293666666669</v>
+        <v>-38.99553166666669</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2178602420391494</v>
+        <v>0.2230741887676085</v>
       </c>
       <c r="T68">
-        <v>2.503686170698275</v>
+        <v>2.579555448598223</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1360661262425364</v>
+        <v>0.1340352885374239</v>
       </c>
       <c r="W68">
-        <v>0.1734779218504987</v>
+        <v>0.1738857140616853</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5442645049701456</v>
+        <v>0.5361411541496957</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1901179107146399</v>
+        <v>0.1916679107146399</v>
       </c>
       <c r="C69">
-        <v>-230.8268423364215</v>
+        <v>-246.000778052248</v>
       </c>
       <c r="D69">
-        <v>432.7981576635786</v>
+        <v>428.1992219477521</v>
       </c>
       <c r="E69">
-        <v>400.0250000000001</v>
+        <v>410.6</v>
       </c>
       <c r="F69">
-        <v>708.5250000000001</v>
+        <v>719.1</v>
       </c>
       <c r="G69">
         <v>44.9</v>
@@ -6951,37 +6951,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M69">
-        <v>142.27182</v>
+        <v>144.39528</v>
       </c>
       <c r="N69">
-        <v>-65.99404222222225</v>
+        <v>-68.11750222222224</v>
       </c>
       <c r="O69">
-        <v>-16.49851055555556</v>
+        <v>-17.02937555555556</v>
       </c>
       <c r="P69">
-        <v>-49.49553166666669</v>
+        <v>-51.08812666666668</v>
       </c>
       <c r="Q69">
-        <v>-38.99553166666669</v>
+        <v>-40.58812666666668</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2230741887676085</v>
+        <v>0.2286140071665962</v>
       </c>
       <c r="T69">
-        <v>2.579555448598223</v>
+        <v>2.660166556366917</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1340352885374239</v>
+        <v>0.1320641813530501</v>
       </c>
       <c r="W69">
-        <v>0.1738857140616853</v>
+        <v>0.1742815123843076</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5361411541496957</v>
+        <v>0.5282567254122001</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1916679107146399</v>
+        <v>0.19321791071464</v>
       </c>
       <c r="C70">
-        <v>-246.000778052248</v>
+        <v>-261.0780043475575</v>
       </c>
       <c r="D70">
-        <v>428.1992219477521</v>
+        <v>423.6969956524426</v>
       </c>
       <c r="E70">
-        <v>410.6</v>
+        <v>421.1750000000001</v>
       </c>
       <c r="F70">
-        <v>719.1</v>
+        <v>729.6750000000001</v>
       </c>
       <c r="G70">
         <v>44.9</v>
@@ -7033,37 +7033,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M70">
-        <v>144.39528</v>
+        <v>146.51874</v>
       </c>
       <c r="N70">
-        <v>-68.11750222222224</v>
+        <v>-70.24096222222224</v>
       </c>
       <c r="O70">
-        <v>-17.02937555555556</v>
+        <v>-17.56024055555556</v>
       </c>
       <c r="P70">
-        <v>-51.08812666666668</v>
+        <v>-52.68072166666668</v>
       </c>
       <c r="Q70">
-        <v>-40.58812666666668</v>
+        <v>-42.18072166666668</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2286140071665962</v>
+        <v>0.2345112332042284</v>
       </c>
       <c r="T70">
-        <v>2.660166556366917</v>
+        <v>2.74597838076585</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1320641813530501</v>
+        <v>0.1301502077102522</v>
       </c>
       <c r="W70">
-        <v>0.1742815123843076</v>
+        <v>0.1746658382917814</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5282567254122001</v>
+        <v>0.5206008308410089</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.19321791071464</v>
+        <v>0.1947679107146399</v>
       </c>
       <c r="C71">
-        <v>-261.0780043475575</v>
+        <v>-276.0615399852715</v>
       </c>
       <c r="D71">
-        <v>423.6969956524426</v>
+        <v>419.2884600147287</v>
       </c>
       <c r="E71">
-        <v>421.1750000000001</v>
+        <v>431.7500000000001</v>
       </c>
       <c r="F71">
-        <v>729.6750000000001</v>
+        <v>740.2500000000001</v>
       </c>
       <c r="G71">
         <v>44.9</v>
@@ -7115,37 +7115,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M71">
-        <v>146.51874</v>
+        <v>148.6422</v>
       </c>
       <c r="N71">
-        <v>-70.24096222222224</v>
+        <v>-72.36442222222226</v>
       </c>
       <c r="O71">
-        <v>-17.56024055555556</v>
+        <v>-18.09110555555556</v>
       </c>
       <c r="P71">
-        <v>-52.68072166666668</v>
+        <v>-54.27331666666669</v>
       </c>
       <c r="Q71">
-        <v>-42.18072166666668</v>
+        <v>-43.77331666666669</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2345112332042284</v>
+        <v>0.2408016076443693</v>
       </c>
       <c r="T71">
-        <v>2.74597838076585</v>
+        <v>2.837510993458045</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1301502077102522</v>
+        <v>0.1282909190286772</v>
       </c>
       <c r="W71">
-        <v>0.1746658382917814</v>
+        <v>0.1750391834590416</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5206008308410089</v>
+        <v>0.5131636761147087</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1947679107146399</v>
+        <v>0.1963179107146399</v>
       </c>
       <c r="C72">
-        <v>-276.0615399852715</v>
+        <v>-290.9542793821126</v>
       </c>
       <c r="D72">
-        <v>419.2884600147287</v>
+        <v>414.9707206178874</v>
       </c>
       <c r="E72">
-        <v>431.7500000000001</v>
+        <v>442.325</v>
       </c>
       <c r="F72">
-        <v>740.2500000000001</v>
+        <v>750.825</v>
       </c>
       <c r="G72">
         <v>44.9</v>
@@ -7197,37 +7197,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M72">
-        <v>148.6422</v>
+        <v>150.76566</v>
       </c>
       <c r="N72">
-        <v>-72.36442222222226</v>
+        <v>-74.48788222222225</v>
       </c>
       <c r="O72">
-        <v>-18.09110555555556</v>
+        <v>-18.62197055555556</v>
       </c>
       <c r="P72">
-        <v>-54.27331666666669</v>
+        <v>-55.86591166666669</v>
       </c>
       <c r="Q72">
-        <v>-43.77331666666669</v>
+        <v>-45.36591166666669</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2408016076443693</v>
+        <v>0.2475258010114166</v>
       </c>
       <c r="T72">
-        <v>2.837510993458045</v>
+        <v>2.935356200129012</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1282909190286772</v>
+        <v>0.1264840046761606</v>
       </c>
       <c r="W72">
-        <v>0.1750391834590416</v>
+        <v>0.175402011861027</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5131636761147087</v>
+        <v>0.5059360187046424</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1963179107146399</v>
+        <v>0.2239246379111027</v>
       </c>
       <c r="C73">
-        <v>-290.9542793821125</v>
+        <v>-365.8437033324644</v>
       </c>
       <c r="D73">
-        <v>414.9707206178874</v>
+        <v>350.6562966675356</v>
       </c>
       <c r="E73">
-        <v>442.3249999999999</v>
+        <v>452.9</v>
       </c>
       <c r="F73">
-        <v>750.8249999999999</v>
+        <v>761.4</v>
       </c>
       <c r="G73">
         <v>44.9</v>
@@ -7279,45 +7279,45 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M73">
-        <v>150.76566</v>
+        <v>179.53812</v>
       </c>
       <c r="N73">
-        <v>-74.48788222222223</v>
+        <v>-103.2603422222222</v>
       </c>
       <c r="O73">
-        <v>-18.62197055555556</v>
+        <v>-25.81508555555556</v>
       </c>
       <c r="P73">
-        <v>-55.86591166666667</v>
+        <v>-77.44525666666667</v>
       </c>
       <c r="Q73">
-        <v>-45.36591166666667</v>
+        <v>-66.94525666666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2475258010114165</v>
+        <v>0.2577900338920484</v>
       </c>
       <c r="T73">
-        <v>2.935356200129012</v>
+        <v>3.084713295129594</v>
       </c>
       <c r="U73">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1264840046761606</v>
+        <v>0.1062139028995315</v>
       </c>
       <c r="W73">
-        <v>0.175402011861027</v>
+        <v>0.2107547616962905</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.5059360187046424</v>
+        <v>0.4248556115981262</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2239246379111027</v>
+        <v>0.2258246379111027</v>
       </c>
       <c r="C74">
-        <v>-365.8437033324644</v>
+        <v>-380.1195687884323</v>
       </c>
       <c r="D74">
-        <v>350.6562966675356</v>
+        <v>346.9554312115678</v>
       </c>
       <c r="E74">
-        <v>452.9</v>
+        <v>463.475</v>
       </c>
       <c r="F74">
-        <v>761.4</v>
+        <v>771.975</v>
       </c>
       <c r="G74">
         <v>44.9</v>
@@ -7361,37 +7361,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M74">
-        <v>179.53812</v>
+        <v>182.031705</v>
       </c>
       <c r="N74">
-        <v>-103.2603422222222</v>
+        <v>-105.7539272222222</v>
       </c>
       <c r="O74">
-        <v>-25.81508555555556</v>
+        <v>-26.43848180555556</v>
       </c>
       <c r="P74">
-        <v>-77.44525666666667</v>
+        <v>-79.31544541666668</v>
       </c>
       <c r="Q74">
-        <v>-66.94525666666667</v>
+        <v>-68.81544541666668</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2577900338920484</v>
+        <v>0.2656415166287909</v>
       </c>
       <c r="T74">
-        <v>3.084713295129594</v>
+        <v>3.19896193568995</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1062139028995315</v>
+        <v>0.1047589179283051</v>
       </c>
       <c r="W74">
-        <v>0.2107547616962905</v>
+        <v>0.2110978471525057</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4248556115981262</v>
+        <v>0.4190356717132203</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2258246379111027</v>
+        <v>0.2277246379111026</v>
       </c>
       <c r="C75">
-        <v>-380.1195687884323</v>
+        <v>-394.3181314178331</v>
       </c>
       <c r="D75">
-        <v>346.9554312115678</v>
+        <v>343.3318685821669</v>
       </c>
       <c r="E75">
-        <v>463.475</v>
+        <v>474.05</v>
       </c>
       <c r="F75">
-        <v>771.975</v>
+        <v>782.55</v>
       </c>
       <c r="G75">
         <v>44.9</v>
@@ -7443,37 +7443,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M75">
-        <v>182.031705</v>
+        <v>184.52529</v>
       </c>
       <c r="N75">
-        <v>-105.7539272222222</v>
+        <v>-108.2475122222222</v>
       </c>
       <c r="O75">
-        <v>-26.43848180555556</v>
+        <v>-27.06187805555555</v>
       </c>
       <c r="P75">
-        <v>-79.31544541666668</v>
+        <v>-81.18563416666666</v>
       </c>
       <c r="Q75">
-        <v>-68.81544541666668</v>
+        <v>-70.68563416666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2656415166287909</v>
+        <v>0.2740969595760521</v>
       </c>
       <c r="T75">
-        <v>3.19896193568995</v>
+        <v>3.321998933216486</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1047589179283051</v>
+        <v>0.1033432568752199</v>
       </c>
       <c r="W75">
-        <v>0.2110978471525057</v>
+        <v>0.2114316600288231</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4190356717132203</v>
+        <v>0.4133730275008796</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2277246379111026</v>
+        <v>0.2296246379111027</v>
       </c>
       <c r="C76">
-        <v>-394.3181314178331</v>
+        <v>-408.4417882122592</v>
       </c>
       <c r="D76">
-        <v>343.3318685821669</v>
+        <v>339.7832117877408</v>
       </c>
       <c r="E76">
-        <v>474.05</v>
+        <v>484.625</v>
       </c>
       <c r="F76">
-        <v>782.55</v>
+        <v>793.125</v>
       </c>
       <c r="G76">
         <v>44.9</v>
@@ -7525,37 +7525,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M76">
-        <v>184.52529</v>
+        <v>187.018875</v>
       </c>
       <c r="N76">
-        <v>-108.2475122222222</v>
+        <v>-110.7410972222222</v>
       </c>
       <c r="O76">
-        <v>-27.06187805555555</v>
+        <v>-27.68527430555556</v>
       </c>
       <c r="P76">
-        <v>-81.18563416666666</v>
+        <v>-83.05582291666667</v>
       </c>
       <c r="Q76">
-        <v>-70.68563416666666</v>
+        <v>-72.55582291666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2740969595760521</v>
+        <v>0.2832288379590941</v>
       </c>
       <c r="T76">
-        <v>3.321998933216486</v>
+        <v>3.454878890545146</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1033432568752199</v>
+        <v>0.1019653467835503</v>
       </c>
       <c r="W76">
-        <v>0.2114316600288231</v>
+        <v>0.2117565712284389</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4133730275008796</v>
+        <v>0.4078613871342012</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2296246379111027</v>
+        <v>0.2315246379111027</v>
       </c>
       <c r="C77">
-        <v>-408.4417882122592</v>
+        <v>-422.4928380764981</v>
       </c>
       <c r="D77">
-        <v>339.7832117877408</v>
+        <v>336.307161923502</v>
       </c>
       <c r="E77">
-        <v>484.625</v>
+        <v>495.2</v>
       </c>
       <c r="F77">
-        <v>793.125</v>
+        <v>803.7</v>
       </c>
       <c r="G77">
         <v>44.9</v>
@@ -7607,37 +7607,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M77">
-        <v>187.018875</v>
+        <v>189.51246</v>
       </c>
       <c r="N77">
-        <v>-110.7410972222222</v>
+        <v>-113.2346822222222</v>
       </c>
       <c r="O77">
-        <v>-27.68527430555556</v>
+        <v>-28.30867055555556</v>
       </c>
       <c r="P77">
-        <v>-83.05582291666667</v>
+        <v>-84.92601166666668</v>
       </c>
       <c r="Q77">
-        <v>-72.55582291666667</v>
+        <v>-74.42601166666668</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2832288379590941</v>
+        <v>0.2931217062073898</v>
       </c>
       <c r="T77">
-        <v>3.454878890545146</v>
+        <v>3.598832177651194</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1019653467835503</v>
+        <v>0.1006236974837667</v>
       </c>
       <c r="W77">
-        <v>0.2117565712284389</v>
+        <v>0.2120729321333278</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4078613871342012</v>
+        <v>0.4024947899350669</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2315246379111027</v>
+        <v>0.2334246379111027</v>
       </c>
       <c r="C78">
-        <v>-422.4928380764981</v>
+        <v>-436.4734867949644</v>
       </c>
       <c r="D78">
-        <v>336.307161923502</v>
+        <v>332.9015132050356</v>
       </c>
       <c r="E78">
-        <v>495.2</v>
+        <v>505.775</v>
       </c>
       <c r="F78">
-        <v>803.7</v>
+        <v>814.275</v>
       </c>
       <c r="G78">
         <v>44.9</v>
@@ -7689,37 +7689,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M78">
-        <v>189.51246</v>
+        <v>192.006045</v>
       </c>
       <c r="N78">
-        <v>-113.2346822222222</v>
+        <v>-115.7282672222222</v>
       </c>
       <c r="O78">
-        <v>-28.30867055555556</v>
+        <v>-28.93206680555556</v>
       </c>
       <c r="P78">
-        <v>-84.92601166666668</v>
+        <v>-86.79620041666666</v>
       </c>
       <c r="Q78">
-        <v>-74.42601166666668</v>
+        <v>-76.29620041666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2931217062073898</v>
+        <v>0.3038748238685806</v>
       </c>
       <c r="T78">
-        <v>3.598832177651194</v>
+        <v>3.755303141896897</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1006236974837667</v>
+        <v>0.09931689621774378</v>
       </c>
       <c r="W78">
-        <v>0.2120729321333278</v>
+        <v>0.212381075871856</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4024947899350669</v>
+        <v>0.3972675848709751</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2334246379111027</v>
+        <v>0.2353246379111027</v>
       </c>
       <c r="C79">
-        <v>-436.4734867949644</v>
+        <v>-450.3858516993958</v>
       </c>
       <c r="D79">
-        <v>332.9015132050356</v>
+        <v>329.5641483006042</v>
       </c>
       <c r="E79">
-        <v>505.775</v>
+        <v>516.35</v>
       </c>
       <c r="F79">
-        <v>814.275</v>
+        <v>824.85</v>
       </c>
       <c r="G79">
         <v>44.9</v>
@@ -7771,37 +7771,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M79">
-        <v>192.006045</v>
+        <v>194.49963</v>
       </c>
       <c r="N79">
-        <v>-115.7282672222222</v>
+        <v>-118.2218522222223</v>
       </c>
       <c r="O79">
-        <v>-28.93206680555556</v>
+        <v>-29.55546305555556</v>
       </c>
       <c r="P79">
-        <v>-86.79620041666666</v>
+        <v>-88.66638916666669</v>
       </c>
       <c r="Q79">
-        <v>-76.29620041666666</v>
+        <v>-78.16638916666669</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3038748238685806</v>
+        <v>0.3156054976807889</v>
       </c>
       <c r="T79">
-        <v>3.755303141896897</v>
+        <v>3.925998739255848</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09931689621774378</v>
+        <v>0.09804360267649065</v>
       </c>
       <c r="W79">
-        <v>0.212381075871856</v>
+        <v>0.2126813184888835</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3972675848709751</v>
+        <v>0.3921744107059626</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2353246379111027</v>
+        <v>0.2372246379111027</v>
       </c>
       <c r="C80">
-        <v>-450.3858516993958</v>
+        <v>-464.2319660585721</v>
       </c>
       <c r="D80">
-        <v>329.5641483006042</v>
+        <v>326.293033941428</v>
       </c>
       <c r="E80">
-        <v>516.35</v>
+        <v>526.9250000000001</v>
       </c>
       <c r="F80">
-        <v>824.85</v>
+        <v>835.4250000000001</v>
       </c>
       <c r="G80">
         <v>44.9</v>
@@ -7853,37 +7853,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M80">
-        <v>194.49963</v>
+        <v>196.993215</v>
       </c>
       <c r="N80">
-        <v>-118.2218522222223</v>
+        <v>-120.7154372222222</v>
       </c>
       <c r="O80">
-        <v>-29.55546305555556</v>
+        <v>-30.17885930555556</v>
       </c>
       <c r="P80">
-        <v>-88.66638916666669</v>
+        <v>-90.53657791666669</v>
       </c>
       <c r="Q80">
-        <v>-78.16638916666669</v>
+        <v>-80.03657791666669</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3156054976807889</v>
+        <v>0.3284533785227312</v>
       </c>
       <c r="T80">
-        <v>3.925998739255848</v>
+        <v>4.112951060172793</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09804360267649065</v>
+        <v>0.09680254441476292</v>
       </c>
       <c r="W80">
-        <v>0.2126813184888835</v>
+        <v>0.2129739600269989</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3921744107059626</v>
+        <v>0.3872101776590516</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2372246379111027</v>
+        <v>0.2391246379111027</v>
       </c>
       <c r="C81">
-        <v>-464.2319660585721</v>
+        <v>-478.0137832091817</v>
       </c>
       <c r="D81">
-        <v>326.293033941428</v>
+        <v>323.0862167908183</v>
       </c>
       <c r="E81">
-        <v>526.9250000000001</v>
+        <v>537.5</v>
       </c>
       <c r="F81">
-        <v>835.4250000000001</v>
+        <v>846</v>
       </c>
       <c r="G81">
         <v>44.9</v>
@@ -7935,37 +7935,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M81">
-        <v>196.993215</v>
+        <v>199.4868</v>
       </c>
       <c r="N81">
-        <v>-120.7154372222222</v>
+        <v>-123.2090222222222</v>
       </c>
       <c r="O81">
-        <v>-30.17885930555556</v>
+        <v>-30.80225555555556</v>
       </c>
       <c r="P81">
-        <v>-90.53657791666669</v>
+        <v>-92.40676666666668</v>
       </c>
       <c r="Q81">
-        <v>-80.03657791666669</v>
+        <v>-81.90676666666668</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3284533785227312</v>
+        <v>0.3425860474488678</v>
       </c>
       <c r="T81">
-        <v>4.112951060172793</v>
+        <v>4.318598613181432</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.09680254441476292</v>
+        <v>0.09559251260957838</v>
       </c>
       <c r="W81">
-        <v>0.2129739600269989</v>
+        <v>0.2132592855266614</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3872101776590516</v>
+        <v>0.3823700504383135</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2391246379111027</v>
+        <v>0.2410246379111027</v>
       </c>
       <c r="C82">
-        <v>-478.0137832091817</v>
+        <v>-491.7331804454676</v>
       </c>
       <c r="D82">
-        <v>323.0862167908183</v>
+        <v>319.9418195545325</v>
       </c>
       <c r="E82">
-        <v>537.5</v>
+        <v>548.075</v>
       </c>
       <c r="F82">
-        <v>846</v>
+        <v>856.575</v>
       </c>
       <c r="G82">
         <v>44.9</v>
@@ -8017,37 +8017,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M82">
-        <v>199.4868</v>
+        <v>201.980385</v>
       </c>
       <c r="N82">
-        <v>-123.2090222222222</v>
+        <v>-125.7026072222222</v>
       </c>
       <c r="O82">
-        <v>-30.80225555555556</v>
+        <v>-31.42565180555556</v>
       </c>
       <c r="P82">
-        <v>-92.40676666666668</v>
+        <v>-94.27695541666668</v>
       </c>
       <c r="Q82">
-        <v>-81.90676666666668</v>
+        <v>-83.77695541666668</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3425860474488678</v>
+        <v>0.3582063657356503</v>
       </c>
       <c r="T82">
-        <v>4.318598613181432</v>
+        <v>4.545893277033088</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09559251260957838</v>
+        <v>0.09441235813291693</v>
       </c>
       <c r="W82">
-        <v>0.2132592855266614</v>
+        <v>0.2135375659522582</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3823700504383135</v>
+        <v>0.3776494325316677</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2410246379111027</v>
+        <v>0.2429246379111027</v>
       </c>
       <c r="C83">
-        <v>-491.7331804454676</v>
+        <v>-505.3919626839302</v>
       </c>
       <c r="D83">
-        <v>319.9418195545325</v>
+        <v>316.85803731607</v>
       </c>
       <c r="E83">
-        <v>548.075</v>
+        <v>558.6500000000001</v>
       </c>
       <c r="F83">
-        <v>856.575</v>
+        <v>867.1500000000001</v>
       </c>
       <c r="G83">
         <v>44.9</v>
@@ -8099,37 +8099,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M83">
-        <v>201.980385</v>
+        <v>204.47397</v>
       </c>
       <c r="N83">
-        <v>-125.7026072222222</v>
+        <v>-128.1961922222223</v>
       </c>
       <c r="O83">
-        <v>-31.42565180555556</v>
+        <v>-32.04904805555557</v>
       </c>
       <c r="P83">
-        <v>-94.27695541666668</v>
+        <v>-96.14714416666669</v>
       </c>
       <c r="Q83">
-        <v>-83.77695541666668</v>
+        <v>-85.64714416666669</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3582063657356503</v>
+        <v>0.3755622749431864</v>
       </c>
       <c r="T83">
-        <v>4.545893277033088</v>
+        <v>4.798442903534926</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09441235813291693</v>
+        <v>0.09326098791178378</v>
       </c>
       <c r="W83">
-        <v>0.2135375659522582</v>
+        <v>0.2138090590504014</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3776494325316677</v>
+        <v>0.3730439516471351</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2429246379111027</v>
+        <v>0.2448246379111027</v>
       </c>
       <c r="C84">
-        <v>-505.3919626839302</v>
+        <v>-518.9918659181187</v>
       </c>
       <c r="D84">
-        <v>316.85803731607</v>
+        <v>313.8331340818813</v>
       </c>
       <c r="E84">
-        <v>558.6500000000001</v>
+        <v>569.225</v>
       </c>
       <c r="F84">
-        <v>867.1500000000001</v>
+        <v>877.725</v>
       </c>
       <c r="G84">
         <v>44.9</v>
@@ -8181,37 +8181,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M84">
-        <v>204.47397</v>
+        <v>206.967555</v>
       </c>
       <c r="N84">
-        <v>-128.1961922222223</v>
+        <v>-130.6897772222222</v>
       </c>
       <c r="O84">
-        <v>-32.04904805555557</v>
+        <v>-32.67244430555556</v>
       </c>
       <c r="P84">
-        <v>-96.14714416666669</v>
+        <v>-98.01733291666667</v>
       </c>
       <c r="Q84">
-        <v>-85.64714416666669</v>
+        <v>-87.51733291666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3755622749431864</v>
+        <v>0.3949600558221974</v>
       </c>
       <c r="T84">
-        <v>4.798442903534926</v>
+        <v>5.080704250801686</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09326098791178378</v>
+        <v>0.09213736155140086</v>
       </c>
       <c r="W84">
-        <v>0.2138090590504014</v>
+        <v>0.2140740101461797</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3730439516471351</v>
+        <v>0.3685494462056035</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2448246379111027</v>
+        <v>0.2467246379111027</v>
       </c>
       <c r="C85">
-        <v>-518.9918659181187</v>
+        <v>-532.5345604774062</v>
       </c>
       <c r="D85">
-        <v>313.8331340818813</v>
+        <v>310.8654395225939</v>
       </c>
       <c r="E85">
-        <v>569.225</v>
+        <v>579.8000000000001</v>
       </c>
       <c r="F85">
-        <v>877.725</v>
+        <v>888.3000000000001</v>
       </c>
       <c r="G85">
         <v>44.9</v>
@@ -8263,37 +8263,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M85">
-        <v>206.967555</v>
+        <v>209.46114</v>
       </c>
       <c r="N85">
-        <v>-130.6897772222222</v>
+        <v>-133.1833622222223</v>
       </c>
       <c r="O85">
-        <v>-32.67244430555556</v>
+        <v>-33.29584055555556</v>
       </c>
       <c r="P85">
-        <v>-98.01733291666667</v>
+        <v>-99.88752166666669</v>
       </c>
       <c r="Q85">
-        <v>-87.51733291666667</v>
+        <v>-89.38752166666669</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3949600558221974</v>
+        <v>0.4167825593110849</v>
       </c>
       <c r="T85">
-        <v>5.080704250801686</v>
+        <v>5.398248266476793</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09213736155140086</v>
+        <v>0.09104048819959845</v>
       </c>
       <c r="W85">
-        <v>0.2140740101461797</v>
+        <v>0.2143326528825347</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3685494462056035</v>
+        <v>0.3641619527983938</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2467246379111027</v>
+        <v>0.2486246379111027</v>
       </c>
       <c r="C86">
-        <v>-532.5345604774061</v>
+        <v>-546.0216541025987</v>
       </c>
       <c r="D86">
-        <v>310.8654395225939</v>
+        <v>307.9533458974013</v>
       </c>
       <c r="E86">
-        <v>579.8</v>
+        <v>590.375</v>
       </c>
       <c r="F86">
-        <v>888.3</v>
+        <v>898.875</v>
       </c>
       <c r="G86">
         <v>44.9</v>
@@ -8345,37 +8345,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M86">
-        <v>209.46114</v>
+        <v>211.954725</v>
       </c>
       <c r="N86">
-        <v>-133.1833622222222</v>
+        <v>-135.6769472222222</v>
       </c>
       <c r="O86">
-        <v>-33.29584055555556</v>
+        <v>-33.91923680555556</v>
       </c>
       <c r="P86">
-        <v>-99.88752166666667</v>
+        <v>-101.7577104166667</v>
       </c>
       <c r="Q86">
-        <v>-89.38752166666667</v>
+        <v>-91.25771041666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4167825593110847</v>
+        <v>0.4415147299318236</v>
       </c>
       <c r="T86">
-        <v>5.39824826647679</v>
+        <v>5.758131484241909</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09104048819959847</v>
+        <v>0.08996942363254437</v>
       </c>
       <c r="W86">
-        <v>0.2143326528825347</v>
+        <v>0.2145852099074461</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3641619527983939</v>
+        <v>0.3598776945301775</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2486246379111027</v>
+        <v>0.2505246379111027</v>
       </c>
       <c r="C87">
-        <v>-546.0216541025987</v>
+        <v>-559.4546948502841</v>
       </c>
       <c r="D87">
-        <v>307.9533458974013</v>
+        <v>305.0953051497158</v>
       </c>
       <c r="E87">
-        <v>590.375</v>
+        <v>600.9499999999999</v>
       </c>
       <c r="F87">
-        <v>898.875</v>
+        <v>909.4499999999999</v>
       </c>
       <c r="G87">
         <v>44.9</v>
@@ -8427,37 +8427,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M87">
-        <v>211.954725</v>
+        <v>214.44831</v>
       </c>
       <c r="N87">
-        <v>-135.6769472222222</v>
+        <v>-138.1705322222222</v>
       </c>
       <c r="O87">
-        <v>-33.91923680555556</v>
+        <v>-34.54263305555556</v>
       </c>
       <c r="P87">
-        <v>-101.7577104166667</v>
+        <v>-103.6278991666667</v>
       </c>
       <c r="Q87">
-        <v>-91.25771041666667</v>
+        <v>-93.12789916666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4415147299318236</v>
+        <v>0.4697800677840967</v>
       </c>
       <c r="T87">
-        <v>5.758131484241909</v>
+        <v>6.169426590259188</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08996942363254437</v>
+        <v>0.08892326754379386</v>
       </c>
       <c r="W87">
-        <v>0.2145852099074461</v>
+        <v>0.2148318935131734</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3598776945301775</v>
+        <v>0.3556930701751754</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2505246379111027</v>
+        <v>0.2524246379111027</v>
       </c>
       <c r="C88">
-        <v>-559.4546948502841</v>
+        <v>-572.8351738369375</v>
       </c>
       <c r="D88">
-        <v>305.0953051497158</v>
+        <v>302.2898261630625</v>
       </c>
       <c r="E88">
-        <v>600.9499999999999</v>
+        <v>611.525</v>
       </c>
       <c r="F88">
-        <v>909.4499999999999</v>
+        <v>920.025</v>
       </c>
       <c r="G88">
         <v>44.9</v>
@@ -8509,37 +8509,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M88">
-        <v>214.44831</v>
+        <v>216.941895</v>
       </c>
       <c r="N88">
-        <v>-138.1705322222222</v>
+        <v>-140.6641172222222</v>
       </c>
       <c r="O88">
-        <v>-34.54263305555556</v>
+        <v>-35.16602930555556</v>
       </c>
       <c r="P88">
-        <v>-103.6278991666667</v>
+        <v>-105.4980879166667</v>
       </c>
       <c r="Q88">
-        <v>-93.12789916666667</v>
+        <v>-94.99808791666669</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4697800677840967</v>
+        <v>0.5023939191521041</v>
       </c>
       <c r="T88">
-        <v>6.169426590259188</v>
+        <v>6.643997866432971</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08892326754379386</v>
+        <v>0.08790116102030196</v>
       </c>
       <c r="W88">
-        <v>0.2148318935131734</v>
+        <v>0.2150729062314128</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3556930701751754</v>
+        <v>0.3516046440812078</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2524246379111027</v>
+        <v>0.2543246379111027</v>
       </c>
       <c r="C89">
-        <v>-572.8351738369375</v>
+        <v>-586.1645278330092</v>
       </c>
       <c r="D89">
-        <v>302.2898261630625</v>
+        <v>299.5354721669909</v>
       </c>
       <c r="E89">
-        <v>611.525</v>
+        <v>622.1</v>
       </c>
       <c r="F89">
-        <v>920.025</v>
+        <v>930.6</v>
       </c>
       <c r="G89">
         <v>44.9</v>
@@ -8591,37 +8591,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M89">
-        <v>216.941895</v>
+        <v>219.43548</v>
       </c>
       <c r="N89">
-        <v>-140.6641172222222</v>
+        <v>-143.1577022222222</v>
       </c>
       <c r="O89">
-        <v>-35.16602930555556</v>
+        <v>-35.78942555555556</v>
       </c>
       <c r="P89">
-        <v>-105.4980879166667</v>
+        <v>-107.3682766666667</v>
       </c>
       <c r="Q89">
-        <v>-94.99808791666669</v>
+        <v>-96.86827666666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5023939191521041</v>
+        <v>0.5404434124147796</v>
       </c>
       <c r="T89">
-        <v>6.643997866432971</v>
+        <v>7.197664355302387</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08790116102030196</v>
+        <v>0.0869022841905258</v>
       </c>
       <c r="W89">
-        <v>0.2150729062314128</v>
+        <v>0.215308441387874</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3516046440812078</v>
+        <v>0.3476091367621033</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2543246379111027</v>
+        <v>0.2562246379111027</v>
       </c>
       <c r="C90">
-        <v>-586.1645278330092</v>
+        <v>-599.4441417164734</v>
       </c>
       <c r="D90">
-        <v>299.5354721669909</v>
+        <v>296.8308582835267</v>
       </c>
       <c r="E90">
-        <v>622.1</v>
+        <v>632.6750000000001</v>
       </c>
       <c r="F90">
-        <v>930.6</v>
+        <v>941.1750000000001</v>
       </c>
       <c r="G90">
         <v>44.9</v>
@@ -8673,37 +8673,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M90">
-        <v>219.43548</v>
+        <v>221.929065</v>
       </c>
       <c r="N90">
-        <v>-143.1577022222222</v>
+        <v>-145.6512872222223</v>
       </c>
       <c r="O90">
-        <v>-35.78942555555556</v>
+        <v>-36.41282180555557</v>
       </c>
       <c r="P90">
-        <v>-107.3682766666667</v>
+        <v>-109.2384654166667</v>
       </c>
       <c r="Q90">
-        <v>-96.86827666666667</v>
+        <v>-98.7384654166667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5404434124147796</v>
+        <v>0.5854109953615777</v>
       </c>
       <c r="T90">
-        <v>7.197664355302387</v>
+        <v>7.851997478511695</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0869022841905258</v>
+        <v>0.08592585403108169</v>
       </c>
       <c r="W90">
-        <v>0.215308441387874</v>
+        <v>0.215538683619471</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3476091367621033</v>
+        <v>0.3437034161243268</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2562246379111027</v>
+        <v>0.2581246379111027</v>
       </c>
       <c r="C91">
-        <v>-599.4441417164734</v>
+        <v>-612.6753507946435</v>
       </c>
       <c r="D91">
-        <v>296.8308582835267</v>
+        <v>294.1746492053565</v>
       </c>
       <c r="E91">
-        <v>632.6750000000001</v>
+        <v>643.25</v>
       </c>
       <c r="F91">
-        <v>941.1750000000001</v>
+        <v>951.75</v>
       </c>
       <c r="G91">
         <v>44.9</v>
@@ -8755,37 +8755,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M91">
-        <v>221.929065</v>
+        <v>224.42265</v>
       </c>
       <c r="N91">
-        <v>-145.6512872222223</v>
+        <v>-148.1448722222222</v>
       </c>
       <c r="O91">
-        <v>-36.41282180555557</v>
+        <v>-37.03621805555556</v>
       </c>
       <c r="P91">
-        <v>-109.2384654166667</v>
+        <v>-111.1086541666667</v>
       </c>
       <c r="Q91">
-        <v>-98.7384654166667</v>
+        <v>-100.6086541666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5854109953615777</v>
+        <v>0.6393720948977355</v>
       </c>
       <c r="T91">
-        <v>7.851997478511695</v>
+        <v>8.637197226362865</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08592585403108169</v>
+        <v>0.08497112231962524</v>
       </c>
       <c r="W91">
-        <v>0.215538683619471</v>
+        <v>0.2157638093570324</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3437034161243268</v>
+        <v>0.3398844892785009</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2581246379111027</v>
+        <v>0.2600246379111027</v>
       </c>
       <c r="C92">
-        <v>-612.6753507946435</v>
+        <v>-625.8594430024322</v>
       </c>
       <c r="D92">
-        <v>294.1746492053565</v>
+        <v>291.5655569975679</v>
       </c>
       <c r="E92">
-        <v>643.25</v>
+        <v>653.825</v>
       </c>
       <c r="F92">
-        <v>951.75</v>
+        <v>962.325</v>
       </c>
       <c r="G92">
         <v>44.9</v>
@@ -8837,37 +8837,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M92">
-        <v>224.42265</v>
+        <v>226.916235</v>
       </c>
       <c r="N92">
-        <v>-148.1448722222222</v>
+        <v>-150.6384572222223</v>
       </c>
       <c r="O92">
-        <v>-37.03621805555556</v>
+        <v>-37.65961430555556</v>
       </c>
       <c r="P92">
-        <v>-111.1086541666667</v>
+        <v>-112.9788429166667</v>
       </c>
       <c r="Q92">
-        <v>-100.6086541666667</v>
+        <v>-102.4788429166667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6393720948977355</v>
+        <v>0.7053245498863729</v>
       </c>
       <c r="T92">
-        <v>8.637197226362865</v>
+        <v>9.596885807069853</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08497112231962524</v>
+        <v>0.08403737372270627</v>
       </c>
       <c r="W92">
-        <v>0.2157638093570324</v>
+        <v>0.2159839872761859</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3398844892785009</v>
+        <v>0.3361494948908251</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2600246379111027</v>
+        <v>0.2619246379111027</v>
       </c>
       <c r="C93">
-        <v>-625.8594430024322</v>
+        <v>-638.9976609846561</v>
       </c>
       <c r="D93">
-        <v>291.5655569975679</v>
+        <v>289.002339015344</v>
       </c>
       <c r="E93">
-        <v>653.825</v>
+        <v>664.4000000000001</v>
       </c>
       <c r="F93">
-        <v>962.325</v>
+        <v>972.9000000000001</v>
       </c>
       <c r="G93">
         <v>44.9</v>
@@ -8919,37 +8919,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M93">
-        <v>226.916235</v>
+        <v>229.40982</v>
       </c>
       <c r="N93">
-        <v>-150.6384572222223</v>
+        <v>-153.1320422222223</v>
       </c>
       <c r="O93">
-        <v>-37.65961430555556</v>
+        <v>-38.28301055555556</v>
       </c>
       <c r="P93">
-        <v>-112.9788429166667</v>
+        <v>-114.8490316666667</v>
       </c>
       <c r="Q93">
-        <v>-102.4788429166667</v>
+        <v>-104.3490316666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7053245498863729</v>
+        <v>0.7877651186221696</v>
       </c>
       <c r="T93">
-        <v>9.596885807069853</v>
+        <v>10.79649653295358</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08403737372270627</v>
+        <v>0.08312392400832903</v>
       </c>
       <c r="W93">
-        <v>0.2159839872761859</v>
+        <v>0.216199378718836</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3361494948908251</v>
+        <v>0.3324956960333161</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2619246379111027</v>
+        <v>0.2638246379111027</v>
       </c>
       <c r="C94">
-        <v>-638.9976609846561</v>
+        <v>-652.0912040694657</v>
       </c>
       <c r="D94">
-        <v>289.002339015344</v>
+        <v>286.4837959305343</v>
       </c>
       <c r="E94">
-        <v>664.4000000000001</v>
+        <v>674.975</v>
       </c>
       <c r="F94">
-        <v>972.9000000000001</v>
+        <v>983.475</v>
       </c>
       <c r="G94">
         <v>44.9</v>
@@ -9001,37 +9001,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M94">
-        <v>229.40982</v>
+        <v>231.903405</v>
       </c>
       <c r="N94">
-        <v>-153.1320422222223</v>
+        <v>-155.6256272222222</v>
       </c>
       <c r="O94">
-        <v>-38.28301055555556</v>
+        <v>-38.90640680555556</v>
       </c>
       <c r="P94">
-        <v>-114.8490316666667</v>
+        <v>-116.7192204166667</v>
       </c>
       <c r="Q94">
-        <v>-104.3490316666667</v>
+        <v>-106.2192204166667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7877651186221696</v>
+        <v>0.8937601355681939</v>
       </c>
       <c r="T94">
-        <v>10.79649653295358</v>
+        <v>12.33885318051838</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08312392400832903</v>
+        <v>0.08223011837383087</v>
       </c>
       <c r="W94">
-        <v>0.216199378718836</v>
+        <v>0.2164101380874507</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3324956960333161</v>
+        <v>0.3289204734953235</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2638246379111027</v>
+        <v>0.2657246379111027</v>
       </c>
       <c r="C95">
-        <v>-652.0912040694657</v>
+        <v>-665.1412301394782</v>
       </c>
       <c r="D95">
-        <v>286.4837959305343</v>
+        <v>284.0087698605219</v>
       </c>
       <c r="E95">
-        <v>674.975</v>
+        <v>685.5500000000001</v>
       </c>
       <c r="F95">
-        <v>983.475</v>
+        <v>994.0500000000001</v>
       </c>
       <c r="G95">
         <v>44.9</v>
@@ -9083,37 +9083,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M95">
-        <v>231.903405</v>
+        <v>234.39699</v>
       </c>
       <c r="N95">
-        <v>-155.6256272222222</v>
+        <v>-158.1192122222222</v>
       </c>
       <c r="O95">
-        <v>-38.90640680555556</v>
+        <v>-39.52980305555556</v>
       </c>
       <c r="P95">
-        <v>-116.7192204166667</v>
+        <v>-118.5894091666667</v>
       </c>
       <c r="Q95">
-        <v>-106.2192204166667</v>
+        <v>-108.0894091666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8937601355681939</v>
+        <v>1.03508682482956</v>
       </c>
       <c r="T95">
-        <v>12.33885318051838</v>
+        <v>14.39532871060479</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08223011837383087</v>
+        <v>0.08135532988049224</v>
       </c>
       <c r="W95">
-        <v>0.2164101380874507</v>
+        <v>0.21661641321418</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3289204734953235</v>
+        <v>0.325421319521969</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2657246379111027</v>
+        <v>0.2676246379111027</v>
       </c>
       <c r="C96">
-        <v>-665.1412301394782</v>
+        <v>-678.1488574067489</v>
       </c>
       <c r="D96">
-        <v>284.0087698605219</v>
+        <v>281.5761425932512</v>
       </c>
       <c r="E96">
-        <v>685.5500000000001</v>
+        <v>696.1250000000001</v>
       </c>
       <c r="F96">
-        <v>994.0500000000001</v>
+        <v>1004.625</v>
       </c>
       <c r="G96">
         <v>44.9</v>
@@ -9165,37 +9165,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M96">
-        <v>234.39699</v>
+        <v>236.890575</v>
       </c>
       <c r="N96">
-        <v>-158.1192122222222</v>
+        <v>-160.6127972222223</v>
       </c>
       <c r="O96">
-        <v>-39.52980305555556</v>
+        <v>-40.15319930555557</v>
       </c>
       <c r="P96">
-        <v>-118.5894091666667</v>
+        <v>-120.4595979166667</v>
       </c>
       <c r="Q96">
-        <v>-108.0894091666667</v>
+        <v>-109.9595979166667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.03508682482956</v>
+        <v>1.232944189795473</v>
       </c>
       <c r="T96">
-        <v>14.39532871060479</v>
+        <v>17.27439445272575</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08135532988049224</v>
+        <v>0.08049895798701337</v>
       </c>
       <c r="W96">
-        <v>0.21661641321418</v>
+        <v>0.2168183457066623</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.325421319521969</v>
+        <v>0.3219958319480535</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2676246379111027</v>
+        <v>0.2695246379111027</v>
       </c>
       <c r="C97">
-        <v>-678.1488574067489</v>
+        <v>-691.1151660972998</v>
       </c>
       <c r="D97">
-        <v>281.5761425932512</v>
+        <v>279.1848339027002</v>
       </c>
       <c r="E97">
-        <v>696.1250000000001</v>
+        <v>706.7</v>
       </c>
       <c r="F97">
-        <v>1004.625</v>
+        <v>1015.2</v>
       </c>
       <c r="G97">
         <v>44.9</v>
@@ -9247,37 +9247,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M97">
-        <v>236.890575</v>
+        <v>239.38416</v>
       </c>
       <c r="N97">
-        <v>-160.6127972222223</v>
+        <v>-163.1063822222222</v>
       </c>
       <c r="O97">
-        <v>-40.15319930555557</v>
+        <v>-40.77659555555556</v>
       </c>
       <c r="P97">
-        <v>-120.4595979166667</v>
+        <v>-122.3297866666667</v>
       </c>
       <c r="Q97">
-        <v>-109.9595979166667</v>
+        <v>-111.8297866666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.232944189795473</v>
+        <v>1.529730237244342</v>
       </c>
       <c r="T97">
-        <v>17.27439445272575</v>
+        <v>21.5929930659072</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08049895798701337</v>
+        <v>0.07966042717464866</v>
       </c>
       <c r="W97">
-        <v>0.2168183457066623</v>
+        <v>0.2170160712722179</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3219958319480535</v>
+        <v>0.3186417086985947</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2695246379111027</v>
+        <v>0.2714246379111027</v>
       </c>
       <c r="C98">
-        <v>-691.1151660972997</v>
+        <v>-704.0412000505336</v>
       </c>
       <c r="D98">
-        <v>279.1848339027002</v>
+        <v>276.8337999494663</v>
       </c>
       <c r="E98">
-        <v>706.6999999999999</v>
+        <v>717.2749999999999</v>
       </c>
       <c r="F98">
-        <v>1015.2</v>
+        <v>1025.775</v>
       </c>
       <c r="G98">
         <v>44.9</v>
@@ -9329,37 +9329,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M98">
-        <v>239.38416</v>
+        <v>241.877745</v>
       </c>
       <c r="N98">
-        <v>-163.1063822222222</v>
+        <v>-165.5999672222222</v>
       </c>
       <c r="O98">
-        <v>-40.77659555555555</v>
+        <v>-41.39999180555555</v>
       </c>
       <c r="P98">
-        <v>-122.3297866666666</v>
+        <v>-124.1999754166667</v>
       </c>
       <c r="Q98">
-        <v>-111.8297866666666</v>
+        <v>-113.6999754166667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.529730237244337</v>
+        <v>2.024373649659116</v>
       </c>
       <c r="T98">
-        <v>21.59299306590714</v>
+        <v>28.79065742120952</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07966042717464866</v>
+        <v>0.07883918565738425</v>
       </c>
       <c r="W98">
-        <v>0.2170160712722179</v>
+        <v>0.2172097200219888</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3186417086985947</v>
+        <v>0.3153567426295369</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2714246379111027</v>
+        <v>0.2733246379111027</v>
       </c>
       <c r="C99">
-        <v>-704.0412000505336</v>
+        <v>-716.9279682385111</v>
       </c>
       <c r="D99">
-        <v>276.8337999494663</v>
+        <v>274.5220317614888</v>
       </c>
       <c r="E99">
-        <v>717.2749999999999</v>
+        <v>727.8499999999999</v>
       </c>
       <c r="F99">
-        <v>1025.775</v>
+        <v>1036.35</v>
       </c>
       <c r="G99">
         <v>44.9</v>
@@ -9411,37 +9411,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M99">
-        <v>241.877745</v>
+        <v>244.37133</v>
       </c>
       <c r="N99">
-        <v>-165.5999672222222</v>
+        <v>-168.0935522222222</v>
       </c>
       <c r="O99">
-        <v>-41.39999180555555</v>
+        <v>-42.02338805555556</v>
       </c>
       <c r="P99">
-        <v>-124.1999754166667</v>
+        <v>-126.0701641666667</v>
       </c>
       <c r="Q99">
-        <v>-113.6999754166667</v>
+        <v>-115.5701641666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.024373649659116</v>
+        <v>3.013660474488674</v>
       </c>
       <c r="T99">
-        <v>28.79065742120952</v>
+        <v>43.18598613181428</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07883918565738425</v>
+        <v>0.07803470417108441</v>
       </c>
       <c r="W99">
-        <v>0.2172097200219888</v>
+        <v>0.2173994167564583</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3153567426295369</v>
+        <v>0.3121388166843376</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2733246379111027</v>
+        <v>0.2752246379111027</v>
       </c>
       <c r="C100">
-        <v>-716.9279682385111</v>
+        <v>-729.7764462097348</v>
       </c>
       <c r="D100">
-        <v>274.5220317614888</v>
+        <v>272.2485537902652</v>
       </c>
       <c r="E100">
-        <v>727.8499999999999</v>
+        <v>738.425</v>
       </c>
       <c r="F100">
-        <v>1036.35</v>
+        <v>1046.925</v>
       </c>
       <c r="G100">
         <v>44.9</v>
@@ -9493,37 +9493,37 @@
         <v>76.27777777777777</v>
       </c>
       <c r="M100">
-        <v>244.37133</v>
+        <v>246.864915</v>
       </c>
       <c r="N100">
-        <v>-168.0935522222222</v>
+        <v>-170.5871372222222</v>
       </c>
       <c r="O100">
-        <v>-42.02338805555556</v>
+        <v>-42.64678430555556</v>
       </c>
       <c r="P100">
-        <v>-126.0701641666667</v>
+        <v>-127.9403529166667</v>
       </c>
       <c r="Q100">
-        <v>-115.5701641666667</v>
+        <v>-117.4403529166667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.013660474488674</v>
+        <v>5.981520948977349</v>
       </c>
       <c r="T100">
-        <v>43.18598613181428</v>
+        <v>86.37197226362856</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07803470417108441</v>
+        <v>0.07724647483602294</v>
       </c>
       <c r="W100">
-        <v>0.2173994167564583</v>
+        <v>0.2175852812336658</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3121388166843376</v>
+        <v>0.3089858993440918</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2752246379111027</v>
-      </c>
-      <c r="C101">
-        <v>-729.7764462097348</v>
-      </c>
-      <c r="D101">
-        <v>272.2485537902652</v>
-      </c>
-      <c r="E101">
-        <v>738.425</v>
-      </c>
-      <c r="F101">
-        <v>1046.925</v>
-      </c>
-      <c r="G101">
-        <v>44.9</v>
-      </c>
-      <c r="H101">
-        <v>749</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>86.77777777777777</v>
-      </c>
-      <c r="K101">
-        <v>10.5</v>
-      </c>
-      <c r="L101">
-        <v>76.27777777777777</v>
-      </c>
-      <c r="M101">
-        <v>246.864915</v>
-      </c>
-      <c r="N101">
-        <v>-170.5871372222222</v>
-      </c>
-      <c r="O101">
-        <v>-42.64678430555556</v>
-      </c>
-      <c r="P101">
-        <v>-127.9403529166667</v>
-      </c>
-      <c r="Q101">
-        <v>-117.4403529166667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.981520948977349</v>
-      </c>
-      <c r="T101">
-        <v>86.37197226362856</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07724647483602294</v>
-      </c>
-      <c r="W101">
-        <v>0.2175852812336658</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3089858993440918</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
